--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -1,5 +1,17 @@
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="Videos" sheetId="2" r:id="rId2"/>
+    <sheet name="Comments" sheetId="3" r:id="rId3"/>
+    <sheet name="Themes" sheetId="4" r:id="rId4"/>
+    <sheet name="Action Ideas" sheetId="5" r:id="rId5"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00%"/>
@@ -51,19 +63,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="Videos" sheetId="2" r:id="rId2"/>
-    <sheet name="Comments" sheetId="3" r:id="rId3"/>
-    <sheet name="Themes" sheetId="4" r:id="rId4"/>
-    <sheet name="Action Ideas" sheetId="5" r:id="rId5"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="6" max="6" width="45" customWidth="1"/>
@@ -177,7 +177,7 @@
         <v>Public views total</v>
       </c>
       <c r="B5" s="2">
-        <v>24697</v>
+        <v>24702</v>
       </c>
       <c r="C5" s="2">
         <v/>
@@ -518,7 +518,7 @@
         <v>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D21" s="2">
         <v>13</v>
@@ -622,10 +622,10 @@
         <v>51</v>
       </c>
       <c r="C26" s="2">
-        <v>18415</v>
+        <v>18419</v>
       </c>
       <c r="D26" s="2">
-        <v>361.1</v>
+        <v>361.2</v>
       </c>
       <c r="E26" s="2">
         <v/>
@@ -644,7 +644,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="2">
-        <v>6282</v>
+        <v>6283</v>
       </c>
       <c r="D27" s="2">
         <v>128.2</v>
@@ -663,7 +663,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="9" max="9" width="10" customWidth="1"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
@@ -774,14 +774,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
         <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E3" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0388</v>
+        <v>0.0377</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
@@ -848,7 +848,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
@@ -885,14 +885,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
         <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E6" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0154</v>
+        <v>0.0152</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
@@ -959,7 +959,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D42" s="4">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D43" s="4">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D44" s="4">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D45" s="4">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D46" s="4">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D47" s="4">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D48" s="4">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D49" s="4">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D50" s="4">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D54" s="4">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
@@ -3808,14 +3808,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
         <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E85" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F85" s="2">
         <v>13</v>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>08/29/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>08/29/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>08/27/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>08/27/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>08/26/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
@@ -4429,7 +4429,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="11" max="11" width="55" customWidth="1"/>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="F3" s="2">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F4" s="2">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F5" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F6" s="2">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F7" s="2">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F8" s="2">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F9" s="2">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="F10" s="2">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="F11" s="2">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="F12" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="F13" s="2">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="F14" s="2">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>09/26/2025</t>
         </is>
       </c>
       <c r="F15" s="2">
@@ -5249,7 +5249,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="3" max="3" width="36" customWidth="1"/>
@@ -5292,7 +5292,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5307,7 +5307,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5322,7 +5322,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -5339,7 +5339,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="4" max="4" width="12" customWidth="1"/>

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -152,13 +152,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>Comments fetched</v>
+        <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2">
-        <v>Public comments from exported videos</v>
+        <v>Public YouTube channel subscriber count</v>
       </c>
       <c r="D4" s="2">
         <v/>
@@ -174,13 +174,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>Public views total</v>
+        <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>24702</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v/>
+        <v>Public comments from exported videos</v>
       </c>
       <c r="D5" s="2">
         <v/>
@@ -196,10 +196,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>Public likes total</v>
+        <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>182</v>
+        <v>24704</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -218,10 +218,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>Public comments total</v>
+        <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -240,10 +240,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>Videos with comments</v>
+        <v>Public comments total</v>
       </c>
       <c r="B8" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v/>
@@ -262,10 +262,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>Shorts count</v>
+        <v>Videos with comments</v>
       </c>
       <c r="B9" s="2">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2">
         <v/>
@@ -284,10 +284,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>Long-form count</v>
+        <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -306,10 +306,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v/>
+        <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v/>
+        <v>49</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -328,7 +328,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>Top Videos by Views</v>
+        <v/>
       </c>
       <c r="B12" s="2">
         <v/>
@@ -350,260 +350,260 @@
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>Rank</v>
+        <v>Top Videos by Views</v>
       </c>
       <c r="B13" s="2">
-        <v>Title</v>
+        <v/>
       </c>
       <c r="C13" s="2">
-        <v>Views</v>
+        <v/>
       </c>
       <c r="D13" s="2">
-        <v>Likes</v>
+        <v/>
       </c>
       <c r="E13" s="2">
-        <v>Comments</v>
+        <v/>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>1</v>
+        <v>Rank</v>
       </c>
       <c r="B14" s="2">
-        <v>想要月餅活動紙留言GROUP</v>
+        <v>Title</v>
       </c>
       <c r="C14" s="2">
-        <v>1830</v>
+        <v>Views</v>
       </c>
       <c r="D14" s="2">
-        <v>10</v>
+        <v>Likes</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <v>Comments</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
+        <v>想要月餅活動紙留言GROUP</v>
       </c>
       <c r="C15" s="2">
-        <v>1317</v>
+        <v>1830</v>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
       </c>
       <c r="F15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="2">
-        <v>力玄華語對我的家族其實是外來語 #shorts</v>
+        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
       </c>
       <c r="C16" s="2">
-        <v>1184</v>
+        <v>1317</v>
       </c>
       <c r="D16" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
+        <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C17" s="2">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="D17" s="2">
+        <v>12</v>
+      </c>
+      <c r="E17" s="2">
         <v>3</v>
       </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
       <c r="F17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
+        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
       </c>
       <c r="C18" s="2">
-        <v>1132</v>
+        <v>1177</v>
       </c>
       <c r="D18" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>我的母語是什麼 #shorts</v>
+        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
       </c>
       <c r="C19" s="2">
-        <v>1113</v>
+        <v>1132</v>
       </c>
       <c r="D19" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>如何在海外創造必須用中文的環境 #shorts</v>
+        <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="D20" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2">
-        <v>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</v>
+        <v>如何在海外創造必須用中文的環境 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1074</v>
+        <v>1109</v>
       </c>
       <c r="D21" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
+        <v>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1026</v>
+        <v>1074</v>
       </c>
       <c r="D22" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>真正重要的不是字數而是他能不能讀懂故事 #shorts</v>
+        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
       </c>
       <c r="C23" s="2">
-        <v>978</v>
+        <v>1026</v>
       </c>
       <c r="D23" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v/>
+        <v>10</v>
       </c>
       <c r="B24" s="2">
-        <v/>
+        <v>真正重要的不是字數而是他能不能讀懂故事 #shorts</v>
       </c>
       <c r="C24" s="2">
-        <v/>
+        <v>978</v>
       </c>
       <c r="D24" s="2">
-        <v/>
+        <v>5</v>
       </c>
       <c r="E24" s="2">
-        <v/>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>Format</v>
+        <v/>
       </c>
       <c r="B25" s="2">
-        <v>Count</v>
+        <v/>
       </c>
       <c r="C25" s="2">
-        <v>Views</v>
+        <v/>
       </c>
       <c r="D25" s="2">
-        <v>Avg views</v>
+        <v/>
       </c>
       <c r="E25" s="2">
         <v/>
@@ -616,16 +616,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>Shorts</v>
+        <v>Format</v>
       </c>
       <c r="B26" s="2">
-        <v>51</v>
+        <v>Count</v>
       </c>
       <c r="C26" s="2">
-        <v>18419</v>
+        <v>Views</v>
       </c>
       <c r="D26" s="2">
-        <v>361.2</v>
+        <v>Avg views</v>
       </c>
       <c r="E26" s="2">
         <v/>
@@ -638,16 +638,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>Long-form</v>
+        <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2">
-        <v>6283</v>
+        <v>18420</v>
       </c>
       <c r="D27" s="2">
-        <v>128.2</v>
+        <v>361.2</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -658,8 +658,30 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>Long-form</v>
+      </c>
+      <c r="B28" s="2">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6284</v>
+      </c>
+      <c r="D28" s="2">
+        <v>128.2</v>
+      </c>
+      <c r="E28" s="2">
+        <v/>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F27"/>
+  <autoFilter ref="A1:F28"/>
 </worksheet>
 </file>
 
@@ -1595,7 +1617,7 @@
         <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E25" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F25" s="2">
         <v>8</v>
@@ -2853,7 +2875,7 @@
         <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E59" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F59" s="2">
         <v>1</v>
@@ -2862,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="3">
-        <v>0.0526</v>
+        <v>0.0513</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5292,7 +5314,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5307,7 +5329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B4" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24704</v>
+        <v>24688</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2">
-        <v>18420</v>
+        <v>18481</v>
       </c>
       <c r="D27" s="2">
-        <v>361.2</v>
+        <v>355.4</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2">
-        <v>6284</v>
+        <v>6207</v>
       </c>
       <c r="D28" s="2">
-        <v>128.2</v>
+        <v>129.3</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E2" s="2">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -779,105 +779,105 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E3" s="2">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E4" s="2">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0159</v>
+        <v>0.0377</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E5" s="2">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -886,35 +886,35 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.0065</v>
+        <v>0.0145</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E6" s="2">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -923,146 +923,146 @@
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0152</v>
+        <v>0.0065</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E7" s="2">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>0.0299</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E8" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E9" s="2">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>0.0488</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E10" s="2">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1075,31 +1075,31 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E11" s="2">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1112,114 +1112,114 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E12" s="2">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E13" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E14" s="2">
-        <v>574</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1230,33 +1230,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E15" s="2">
-        <v>39</v>
+        <v>574</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0256</v>
+        <v>0.007</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,33 +1267,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E16" s="2">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E17" s="2">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0089</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E18" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1378,24 +1378,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E19" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -1415,33 +1415,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E20" s="2">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,24 +1452,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E21" s="2">
-        <v>436</v>
+        <v>344</v>
       </c>
       <c r="F21" s="2">
         <v>2</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0046</v>
+        <v>0.0058</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,49 +1489,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E22" s="2">
+        <v>436</v>
+      </c>
+      <c r="F22" s="2">
         <v>2</v>
       </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1540,47 +1540,47 @@
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E23" s="2">
-        <v>215</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0047</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E24" s="2">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0036</v>
+        <v>0.0047</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E25" s="2">
-        <v>1114</v>
+        <v>276</v>
       </c>
       <c r="F25" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.0117</v>
+        <v>0.0036</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E26" s="2">
-        <v>700</v>
+        <v>1114</v>
       </c>
       <c r="F26" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G26" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0043</v>
+        <v>0.0117</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E27" s="2">
-        <v>978</v>
+        <v>700</v>
       </c>
       <c r="F27" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0051</v>
+        <v>0.0043</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E28" s="2">
-        <v>70</v>
+        <v>978</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,24 +1748,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E29" s="2">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
@@ -1785,24 +1785,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E30" s="2">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -1822,24 +1822,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E31" s="2">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
@@ -1859,24 +1859,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E32" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -1889,19 +1889,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1933,12 +1933,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E34" s="2">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -1970,12 +1970,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1984,19 +1984,19 @@
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E35" s="2">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="F35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,12 +2007,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2021,19 +2021,19 @@
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E36" s="2">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E37" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,24 +2081,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E38" s="2">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -2111,40 +2111,40 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E39" s="2">
-        <v>679</v>
+        <v>155</v>
       </c>
       <c r="F39" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2155,49 +2155,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E40" s="2">
-        <v>65</v>
+        <v>679</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2206,204 +2206,204 @@
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E41" s="2">
-        <v>1109</v>
+        <v>65</v>
       </c>
       <c r="F41" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E42" s="2">
-        <v>36</v>
+        <v>1109</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0278</v>
+        <v>0.0027</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E43" s="2">
-        <v>1184</v>
+        <v>36</v>
       </c>
       <c r="F43" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0127</v>
+        <v>0.0278</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E44" s="2">
+        <v>1184</v>
+      </c>
+      <c r="F44" s="2">
         <v>12</v>
       </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
       <c r="G44" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E45" s="2">
-        <v>403</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E46" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="F46" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,24 +2414,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E47" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E48" s="2">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0096</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E49" s="2">
-        <v>1026</v>
+        <v>104</v>
       </c>
       <c r="F49" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0068</v>
+        <v>0.0096</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E50" s="2">
-        <v>50</v>
+        <v>1026</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,24 +2562,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E51" s="2">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2599,12 +2599,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -2629,19 +2629,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E53" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2673,12 +2673,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2687,56 +2687,56 @@
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E54" s="2">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E55" s="2">
-        <v>696</v>
+        <v>1132</v>
       </c>
       <c r="F55" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0.0057</v>
+        <v>0.0062</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,61 +2747,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E56" s="2">
-        <v>15</v>
+        <v>696</v>
       </c>
       <c r="F56" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E57" s="2">
-        <v>333</v>
+        <v>15</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2814,31 +2814,31 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E58" s="2">
-        <v>2</v>
+        <v>333</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -2858,181 +2858,181 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E59" s="2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E60" s="2">
-        <v>1177</v>
+        <v>39</v>
       </c>
       <c r="F60" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0034</v>
+        <v>0.0513</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E61" s="2">
-        <v>35</v>
+        <v>1177</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
       </c>
       <c r="H61" s="3">
-        <v>0.0571</v>
+        <v>0.0034</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E62" s="2">
-        <v>211</v>
+        <v>35</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0047</v>
+        <v>0.0571</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E63" s="2">
-        <v>1317</v>
+        <v>211</v>
       </c>
       <c r="F63" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0114</v>
+        <v>0.0047</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,33 +3043,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E64" s="2">
-        <v>70</v>
+        <v>1317</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,61 +3080,61 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E65" s="2">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F65" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0571</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E66" s="2">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0127</v>
+        <v>0.0571</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,12 +3154,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3168,158 +3168,158 @@
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E67" s="2">
-        <v>531</v>
+        <v>158</v>
       </c>
       <c r="F67" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0113</v>
+        <v>0.0127</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E68" s="2">
-        <v>47</v>
+        <v>531</v>
       </c>
       <c r="F68" s="2">
+        <v>5</v>
+      </c>
+      <c r="G68" s="2">
         <v>1</v>
       </c>
-      <c r="G68" s="2">
-        <v>0</v>
-      </c>
       <c r="H68" s="3">
-        <v>0.0213</v>
+        <v>0.0113</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E69" s="2">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E70" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="F70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E71" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F71" s="2">
         <v>1</v>
@@ -3328,44 +3328,44 @@
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E72" s="2">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="F72" s="2">
         <v>1</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0294</v>
+        <v>0.04</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,107 +3376,107 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E73" s="2">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E74" s="2">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E75" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,70 +3487,70 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E76" s="2">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0316</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E77" s="2">
-        <v>1830</v>
+        <v>95</v>
       </c>
       <c r="F77" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0055</v>
+        <v>0.0316</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,33 +3561,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E78" s="2">
-        <v>6</v>
+        <v>1830</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,12 +3598,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E79" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -3628,77 +3628,77 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E80" s="2">
-        <v>924</v>
+        <v>10</v>
       </c>
       <c r="F80" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E81" s="2">
-        <v>27</v>
+        <v>924</v>
       </c>
       <c r="F81" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.037</v>
+        <v>0.0184</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,33 +3709,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E82" s="2">
-        <v>323</v>
+        <v>27</v>
       </c>
       <c r="F82" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0093</v>
+        <v>0.037</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3746,49 +3746,49 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E83" s="2">
-        <v>100</v>
+        <v>323</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.01</v>
+        <v>0.0093</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3797,130 +3797,130 @@
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E84" s="2">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E85" s="2">
-        <v>1074</v>
+        <v>9</v>
       </c>
       <c r="F85" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E86" s="2">
-        <v>15</v>
+        <v>1074</v>
       </c>
       <c r="F86" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E87" s="2">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,24 +3931,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E88" s="2">
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.0046</v>
+        <v>0.0074</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,33 +3968,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E89" s="2">
-        <v>10</v>
+        <v>217</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E90" s="2">
-        <v>946</v>
+        <v>10</v>
       </c>
       <c r="F90" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,33 +4042,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E91" s="2">
-        <v>20</v>
+        <v>946</v>
       </c>
       <c r="F91" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.05</v>
+        <v>0.0095</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E92" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,33 +4116,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1Vyb1Lt5UOU</t>
+          <t>NwXxciSquSU</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>設定目標  🎯 setting goals～Stephanie</t>
+          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
       </c>
       <c r="E93" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0111</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,33 +4153,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>XPAxt3Tx2D8</t>
+          <t>1Vyb1Lt5UOU</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
+          <t>設定目標  🎯 setting goals～Stephanie</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
       </c>
       <c r="E94" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>0.0111</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,12 +4190,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HDcdYMMnKjY</t>
+          <t>XPAxt3Tx2D8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>當你打開我的相簿📱</t>
+          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
       </c>
       <c r="E95" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -4227,12 +4227,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>vbRmUsUOG6A</t>
+          <t>HDcdYMMnKjY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
+          <t>當你打開我的相簿📱</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
       </c>
       <c r="E96" s="2">
-        <v>16</v>
+        <v>364</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -4264,24 +4264,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>vLW3lKeD1Lw</t>
+          <t>vbRmUsUOG6A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>要更多陪伴孩子學中文的實用點子嗎？💡快來加入【樂樂官方 LINE】，持續分享：✨ 親子共讀小技巧✨ 中文學習資源✨ 最新活動 &amp; 免費下載👉 掃描影片裡的 QR Code</t>
+          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>08/29/2025</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vLW3lKeD1Lw","https://www.youtube.com/watch?v=vLW3lKeD1Lw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
       </c>
       <c r="E97" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -4301,12 +4301,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>QB_An7T2_H0</t>
+          <t>vLW3lKeD1Lw</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>🎒📚 開學季，樂樂家庭會員有專屬福利！👉 這次我們準備了「DIY 書包設計小活動」：✔️ 孩子能自己畫專屬書包</t>
+          <t>要更多陪伴孩子學中文的實用點子嗎？💡快來加入【樂樂官方 LINE】，持續分享：✨ 親子共讀小技巧✨ 中文學習資源✨ 最新活動 &amp; 免費下載👉 掃描影片裡的 QR Code</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QB_An7T2_H0","https://www.youtube.com/watch?v=QB_An7T2_H0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vLW3lKeD1Lw","https://www.youtube.com/watch?v=vLW3lKeD1Lw")</f>
       </c>
       <c r="E98" s="2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -4338,24 +4338,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>pUnv3LnxHIs</t>
+          <t>QB_An7T2_H0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>024｜【樂樂 Talk】如何長期陪孩子一直說下去——面對大魔王階段，海外家長最需要知道的兩件事｜S3E06</t>
+          <t>🎒📚 開學季，樂樂家庭會員有專屬福利！👉 這次我們準備了「DIY 書包設計小活動」：✔️ 孩子能自己畫專屬書包</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>08/27/2025</t>
+          <t>08/29/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pUnv3LnxHIs","https://www.youtube.com/watch?v=pUnv3LnxHIs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QB_An7T2_H0","https://www.youtube.com/watch?v=QB_An7T2_H0")</f>
       </c>
       <c r="E99" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4375,12 +4375,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RJAY7M9ioTA</t>
+          <t>pUnv3LnxHIs</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🍰 去咖啡廳吃蛋糕時，你會點什麼蛋糕呢？</t>
+          <t>024｜【樂樂 Talk】如何長期陪孩子一直說下去——面對大魔王階段，海外家長最需要知道的兩件事｜S3E06</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4389,19 +4389,19 @@
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RJAY7M9ioTA","https://www.youtube.com/watch?v=RJAY7M9ioTA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pUnv3LnxHIs","https://www.youtube.com/watch?v=pUnv3LnxHIs")</f>
       </c>
       <c r="E100" s="2">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="F100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0085</v>
+        <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,24 +4412,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>uX9sY7oUeeI</t>
+          <t>RJAY7M9ioTA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📚 開學小儀式！準備好迎接新學期了嗎？我們特別設計了【樂樂活動紙—開學掛飾】，讓孩子透過 ✂️剪剪貼貼、🎨自由上色，為學習角落增添新氣象</t>
+          <t>🍰 去咖啡廳吃蛋糕時，你會點什麼蛋糕呢？</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>08/26/2025</t>
+          <t>08/27/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uX9sY7oUeeI","https://www.youtube.com/watch?v=uX9sY7oUeeI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RJAY7M9ioTA","https://www.youtube.com/watch?v=RJAY7M9ioTA")</f>
       </c>
       <c r="E101" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.0118</v>
+        <v>0.0085</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -177,7 +177,7 @@
         <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
         <v>Public comments from exported videos</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24688</v>
+        <v>24692</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -243,7 +243,7 @@
         <v>Public comments total</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v/>
@@ -265,7 +265,7 @@
         <v>Videos with comments</v>
       </c>
       <c r="B9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -500,7 +500,7 @@
         <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D20" s="2">
         <v>8</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2">
-        <v>18481</v>
+        <v>18579</v>
       </c>
       <c r="D27" s="2">
-        <v>355.4</v>
+        <v>350.5</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="2">
-        <v>6207</v>
+        <v>6113</v>
       </c>
       <c r="D28" s="2">
-        <v>129.3</v>
+        <v>130.1</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E2" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E3" s="2">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,33 +823,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E4" s="2">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E5" s="2">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,33 +897,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E6" s="2">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0065</v>
+        <v>0.0459</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,33 +934,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E7" s="2">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0.0299</v>
+        <v>0.0137</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -971,33 +971,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E8" s="2">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1008,24 +1008,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E9" s="2">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.0488</v>
+        <v>0.0299</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,24 +1045,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E10" s="2">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1082,33 +1082,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E11" s="2">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E12" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1156,33 +1156,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E13" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E14" s="2">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,70 +1230,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E15" s="2">
-        <v>574</v>
+        <v>21</v>
       </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.007</v>
+        <v>0.0476</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E16" s="2">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0.0256</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E17" s="2">
-        <v>91</v>
+        <v>576</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E18" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1378,24 +1378,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E19" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -1415,33 +1415,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E20" s="2">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E21" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E22" s="2">
-        <v>436</v>
+        <v>271</v>
       </c>
       <c r="F22" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,70 +1526,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E23" s="2">
+        <v>346</v>
+      </c>
+      <c r="F23" s="2">
         <v>2</v>
       </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E24" s="2">
-        <v>215</v>
+        <v>439</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0047</v>
+        <v>0.0046</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,70 +1600,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E25" s="2">
-        <v>276</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E26" s="2">
-        <v>1114</v>
+        <v>216</v>
       </c>
       <c r="F26" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0117</v>
+        <v>0.0046</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E27" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E28" s="2">
-        <v>978</v>
+        <v>1115</v>
       </c>
       <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2">
         <v>5</v>
       </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
       <c r="H28" s="3">
-        <v>0.0051</v>
+        <v>0.0117</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E29" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E30" s="2">
-        <v>179</v>
+        <v>978</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,24 +1822,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E31" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
@@ -1859,24 +1859,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E32" s="2">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -1896,24 +1896,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E33" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1926,31 +1926,31 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E34" s="2">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -1963,19 +1963,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E35" s="2">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2007,12 +2007,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2021,19 +2021,19 @@
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E36" s="2">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E37" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,12 +2081,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E38" s="2">
+        <v>101</v>
+      </c>
+      <c r="F38" s="2">
         <v>1</v>
       </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E39" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2148,68 +2148,68 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E40" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E41" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2222,40 +2222,40 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E42" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F42" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E43" s="2">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,33 +2303,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E44" s="2">
-        <v>1184</v>
+        <v>1109</v>
       </c>
       <c r="F44" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G44" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E45" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,33 +2377,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E46" s="2">
-        <v>403</v>
+        <v>1184</v>
       </c>
       <c r="F46" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G46" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,24 +2414,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E47" s="2">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2444,40 +2444,40 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E48" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F48" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E49" s="2">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0096</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E50" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,33 +2562,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E51" s="2">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,33 +2599,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E52" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F52" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,24 +2636,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E53" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2666,19 +2666,19 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E54" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -2703,19 +2703,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2724,130 +2724,130 @@
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E55" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F55" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E56" s="2">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E57" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E58" s="2">
-        <v>333</v>
+        <v>696</v>
       </c>
       <c r="F58" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,24 +2858,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E59" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2888,77 +2888,77 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E60" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E61" s="2">
-        <v>1177</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2969,24 +2969,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E62" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
@@ -2995,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0571</v>
+        <v>0.0513</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,33 +3006,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E63" s="2">
-        <v>211</v>
+        <v>1177</v>
       </c>
       <c r="F63" s="2">
+        <v>3</v>
+      </c>
+      <c r="G63" s="2">
         <v>1</v>
       </c>
-      <c r="G63" s="2">
-        <v>0</v>
-      </c>
       <c r="H63" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,70 +3043,70 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E64" s="2">
-        <v>1317</v>
+        <v>35</v>
       </c>
       <c r="F64" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0114</v>
+        <v>0.0571</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E65" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,144 +3117,144 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>1317</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0571</v>
+        <v>0.0114</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E67" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E68" s="2">
-        <v>531</v>
+        <v>35</v>
       </c>
       <c r="F68" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0113</v>
+        <v>0.0571</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E69" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,33 +3265,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E70" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F70" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,24 +3302,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E71" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F71" s="2">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E72" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,107 +3376,107 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E73" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F73" s="2">
         <v>1</v>
       </c>
       <c r="G73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E74" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E75" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,24 +3487,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E76" s="2">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -3517,114 +3517,114 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E77" s="2">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="F77" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0316</v>
+        <v>0.0196</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E78" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F78" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0</v>
+        <v>0.0316</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,70 +3635,70 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E80" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F80" s="2">
         <v>10</v>
       </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E81" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F81" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,70 +3709,70 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E82" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E83" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F83" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,24 +3783,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E84" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F84" s="2">
         <v>1</v>
@@ -3809,44 +3809,44 @@
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E85" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,33 +3857,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E86" s="2">
-        <v>1074</v>
+        <v>100</v>
       </c>
       <c r="F86" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,24 +3894,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E87" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -3931,70 +3931,70 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E88" s="2">
-        <v>136</v>
+        <v>1074</v>
       </c>
       <c r="F88" s="2">
+        <v>13</v>
+      </c>
+      <c r="G88" s="2">
         <v>1</v>
       </c>
-      <c r="G88" s="2">
-        <v>0</v>
-      </c>
       <c r="H88" s="3">
-        <v>0.0074</v>
+        <v>0.013</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E89" s="2">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E90" s="2">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,33 +4042,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E91" s="2">
-        <v>946</v>
+        <v>217</v>
       </c>
       <c r="F91" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0095</v>
+        <v>0.0046</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E92" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,33 +4116,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E93" s="2">
-        <v>19</v>
+        <v>947</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,24 +4153,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1Vyb1Lt5UOU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>設定目標  🎯 setting goals～Stephanie</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E94" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.0111</v>
+        <v>0.05</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,24 +4190,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>XPAxt3Tx2D8</t>
+          <t>NwXxciSquSU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
+          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
       </c>
       <c r="E95" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -4227,33 +4227,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HDcdYMMnKjY</t>
+          <t>1Vyb1Lt5UOU</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>當你打開我的相簿📱</t>
+          <t>設定目標  🎯 setting goals～Stephanie</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
       </c>
       <c r="E96" s="2">
-        <v>364</v>
+        <v>90</v>
       </c>
       <c r="F96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>0.0111</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,12 +4264,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>vbRmUsUOG6A</t>
+          <t>XPAxt3Tx2D8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
+          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
       </c>
       <c r="E97" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -4301,24 +4301,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>vLW3lKeD1Lw</t>
+          <t>HDcdYMMnKjY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>要更多陪伴孩子學中文的實用點子嗎？💡快來加入【樂樂官方 LINE】，持續分享：✨ 親子共讀小技巧✨ 中文學習資源✨ 最新活動 &amp; 免費下載👉 掃描影片裡的 QR Code</t>
+          <t>當你打開我的相簿📱</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>08/29/2025</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vLW3lKeD1Lw","https://www.youtube.com/watch?v=vLW3lKeD1Lw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
       </c>
       <c r="E98" s="2">
-        <v>4</v>
+        <v>364</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -4338,24 +4338,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QB_An7T2_H0</t>
+          <t>vbRmUsUOG6A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>🎒📚 開學季，樂樂家庭會員有專屬福利！👉 這次我們準備了「DIY 書包設計小活動」：✔️ 孩子能自己畫專屬書包</t>
+          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>08/29/2025</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QB_An7T2_H0","https://www.youtube.com/watch?v=QB_An7T2_H0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
       </c>
       <c r="E99" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4375,24 +4375,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pUnv3LnxHIs</t>
+          <t>vLW3lKeD1Lw</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>024｜【樂樂 Talk】如何長期陪孩子一直說下去——面對大魔王階段，海外家長最需要知道的兩件事｜S3E06</t>
+          <t>要更多陪伴孩子學中文的實用點子嗎？💡快來加入【樂樂官方 LINE】，持續分享：✨ 親子共讀小技巧✨ 中文學習資源✨ 最新活動 &amp; 免費下載👉 掃描影片裡的 QR Code</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>08/27/2025</t>
+          <t>08/29/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pUnv3LnxHIs","https://www.youtube.com/watch?v=pUnv3LnxHIs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vLW3lKeD1Lw","https://www.youtube.com/watch?v=vLW3lKeD1Lw")</f>
       </c>
       <c r="E100" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F100" s="2">
         <v>0</v>
@@ -4412,33 +4412,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RJAY7M9ioTA</t>
+          <t>QB_An7T2_H0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🍰 去咖啡廳吃蛋糕時，你會點什麼蛋糕呢？</t>
+          <t>🎒📚 開學季，樂樂家庭會員有專屬福利！👉 這次我們準備了「DIY 書包設計小活動」：✔️ 孩子能自己畫專屬書包</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>08/27/2025</t>
+          <t>08/29/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RJAY7M9ioTA","https://www.youtube.com/watch?v=RJAY7M9ioTA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QB_An7T2_H0","https://www.youtube.com/watch?v=QB_An7T2_H0")</f>
       </c>
       <c r="E101" s="2">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="F101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.0085</v>
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>@fet092</t>
+          <t>@yenyanchen2752</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台語就是眾多華語中的一支。</t>
+          <t>❤❤❤</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@peter90004</t>
+          <t>@fet092</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
+          <t>台語就是眾多華語中的一支。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>@frankzheng5494</t>
+          <t>@peter90004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="F4" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>原來就是說閩南語方言啦！</t>
+          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>@arielcc5397</t>
+          <t>@frankzheng5494</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
+          <t>原來就是說閩南語方言啦！</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>@kcma-k9l</t>
+          <t>@arielcc5397</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台独</t>
+          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>政治/爭議</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4785,40 +4785,40 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>@debc8406</t>
+          <t>@kcma-k9l</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
+          <t>台独</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>海外環境, 家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>@suika_hachikai</t>
+          <t>@debc8406</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4867,31 +4867,31 @@
         </is>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>部分正確。</t>
+          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>政治/爭議</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>海外環境, 家庭語言</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@貓星人-c6i</t>
+          <t>@suika_hachikai</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4920,64 +4920,64 @@
         </is>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
+          <t>部分正確。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>@zhenfan2</t>
+          <t>@貓星人-c6i</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>最後兒子亂入是共讀最好示範😅</t>
+          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4987,42 +4987,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>@Lennonrx8</t>
+          <t>@zhenfan2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11/16/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="F11" s="2">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>华文才难学啊，英文太简单了</t>
+          <t>最後兒子亂入是共讀最好示範😅</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5040,37 +5040,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>學習/共讀</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>@QCASo01PegatronUuUsss</t>
+          <t>@Lennonrx8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>❤❤❤❤❤❤❤</t>
+          <t>华文才难学啊，英文太简单了</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5110,25 +5110,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@annieyang6601</t>
+          <t>@QCASo01PegatronUuUsss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="F13" s="2">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>我想共學</t>
+          <t>❤❤❤❤❤❤❤</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5156,23 +5156,23 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>了解整套</t>
+          <t>我想共學</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>學習/共讀</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -5209,65 +5209,118 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>8__o_r_dr4M</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+        </is>
+      </c>
+      <c r="C15" s="4">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>@annieyang6601</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>了解整套</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>未分類</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>1Yp-hUO3SpA</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
-      <c r="C15" s="4">
+      <c r="C16" s="4">
         <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>@心自己嚇自己</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>09/26/2025</t>
         </is>
       </c>
-      <c r="F15" s="2">
+      <c r="F16" s="2">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>？那所以我可以重讀幼兒園了！</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>學習/共讀</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>未分類</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K16"/>
 </worksheet>
 </file>
 
@@ -5314,7 +5367,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5344,7 +5397,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24692</v>
+        <v>24698</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2">
-        <v>18579</v>
+        <v>18580</v>
       </c>
       <c r="D27" s="2">
-        <v>350.5</v>
+        <v>344.1</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="D28" s="2">
-        <v>130.1</v>
+        <v>133</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E2" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E3" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,24 +823,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E4" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E5" s="2">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,33 +897,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E6" s="2">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,33 +934,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E7" s="2">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -971,33 +971,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E8" s="2">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0.0064</v>
+        <v>0.0459</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1008,33 +1008,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E9" s="2">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.0299</v>
+        <v>0.0137</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,33 +1045,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E10" s="2">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1082,24 +1082,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E11" s="2">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0476</v>
+        <v>0.0299</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E12" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1156,33 +1156,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E13" s="2">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E14" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,33 +1230,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E15" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,24 +1267,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,70 +1304,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E17" s="2">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E18" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E19" s="2">
-        <v>92</v>
+        <v>576</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,33 +1415,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E20" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,24 +1452,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E21" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E22" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,33 +1526,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E23" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E24" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,64 +1600,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E26" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -1674,70 +1674,70 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E27" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E28" s="2">
-        <v>1115</v>
+        <v>216</v>
       </c>
       <c r="F28" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.0117</v>
+        <v>0.0046</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E29" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F29" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E30" s="2">
-        <v>978</v>
+        <v>1115</v>
       </c>
       <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
       <c r="H30" s="3">
-        <v>0.0051</v>
+        <v>0.0117</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E31" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,33 +1859,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E32" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,24 +1896,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E33" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1933,24 +1933,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E34" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -1970,24 +1970,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E35" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2000,31 +2000,31 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E36" s="2">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
@@ -2037,19 +2037,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E37" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,12 +2081,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E38" s="2">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,12 +2118,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E39" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,12 +2155,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E40" s="2">
+        <v>101</v>
+      </c>
+      <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,24 +2192,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E41" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2222,68 +2222,68 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E42" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E43" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2296,40 +2296,40 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E44" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F44" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E45" s="2">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,33 +2377,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E46" s="2">
-        <v>1184</v>
+        <v>1109</v>
       </c>
       <c r="F46" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G46" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E47" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E48" s="2">
-        <v>403</v>
+        <v>1184</v>
       </c>
       <c r="F48" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,24 +2488,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E49" s="2">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -2518,40 +2518,40 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E50" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,33 +2562,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E51" s="2">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,33 +2599,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E52" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F52" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,33 +2636,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E53" s="2">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,33 +2673,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E54" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F54" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,24 +2710,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E55" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2740,19 +2740,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E56" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -2777,19 +2777,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2798,130 +2798,130 @@
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E57" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F57" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E58" s="2">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E59" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F59" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E60" s="2">
-        <v>333</v>
+        <v>696</v>
       </c>
       <c r="F60" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2932,24 +2932,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E61" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,77 +2962,77 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E62" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E63" s="2">
-        <v>1177</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,24 +3043,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E64" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F64" s="2">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0571</v>
+        <v>0.0513</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,33 +3080,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E65" s="2">
-        <v>211</v>
+        <v>1177</v>
       </c>
       <c r="F65" s="2">
+        <v>3</v>
+      </c>
+      <c r="G65" s="2">
         <v>1</v>
       </c>
-      <c r="G65" s="2">
-        <v>0</v>
-      </c>
       <c r="H65" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,70 +3117,70 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E66" s="2">
-        <v>1317</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0114</v>
+        <v>0.0571</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E67" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,144 +3191,144 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E68" s="2">
-        <v>35</v>
+        <v>1317</v>
       </c>
       <c r="F68" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0571</v>
+        <v>0.0114</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E69" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F69" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E70" s="2">
-        <v>531</v>
+        <v>35</v>
       </c>
       <c r="F70" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0113</v>
+        <v>0.0571</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E71" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E72" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F72" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,24 +3376,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E73" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F73" s="2">
         <v>1</v>
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,33 +3413,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E74" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3450,107 +3450,107 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E75" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E76" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E77" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F77" s="2">
         <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,24 +3561,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E78" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -3591,114 +3591,114 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E79" s="2">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="F79" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0.0316</v>
+        <v>0.0196</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E80" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F80" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E81" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,70 +3709,70 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E82" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F82" s="2">
         <v>10</v>
       </c>
-      <c r="F82" s="2">
-        <v>0</v>
-      </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E83" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F83" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,70 +3783,70 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E84" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E85" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F85" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,24 +3857,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E86" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F86" s="2">
         <v>1</v>
@@ -3883,44 +3883,44 @@
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E87" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,33 +3931,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E88" s="2">
-        <v>1074</v>
+        <v>100</v>
       </c>
       <c r="F88" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,24 +3968,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E89" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -4005,70 +4005,70 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E90" s="2">
-        <v>136</v>
+        <v>1074</v>
       </c>
       <c r="F90" s="2">
+        <v>13</v>
+      </c>
+      <c r="G90" s="2">
         <v>1</v>
       </c>
-      <c r="G90" s="2">
-        <v>0</v>
-      </c>
       <c r="H90" s="3">
-        <v>0.0074</v>
+        <v>0.013</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E91" s="2">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="F91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E92" s="2">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,33 +4116,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E93" s="2">
-        <v>947</v>
+        <v>217</v>
       </c>
       <c r="F93" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0095</v>
+        <v>0.0046</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,33 +4153,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E94" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,33 +4190,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E95" s="2">
-        <v>19</v>
+        <v>947</v>
       </c>
       <c r="F95" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,24 +4227,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1Vyb1Lt5UOU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>設定目標  🎯 setting goals～Stephanie</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E96" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.0111</v>
+        <v>0.05</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,24 +4264,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>XPAxt3Tx2D8</t>
+          <t>NwXxciSquSU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
+          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
       </c>
       <c r="E97" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -4301,33 +4301,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HDcdYMMnKjY</t>
+          <t>1Vyb1Lt5UOU</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>當你打開我的相簿📱</t>
+          <t>設定目標  🎯 setting goals～Stephanie</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
       </c>
       <c r="E98" s="2">
-        <v>364</v>
+        <v>91</v>
       </c>
       <c r="F98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,12 +4338,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>vbRmUsUOG6A</t>
+          <t>XPAxt3Tx2D8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
+          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
       </c>
       <c r="E99" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4375,24 +4375,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>vLW3lKeD1Lw</t>
+          <t>HDcdYMMnKjY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>要更多陪伴孩子學中文的實用點子嗎？💡快來加入【樂樂官方 LINE】，持續分享：✨ 親子共讀小技巧✨ 中文學習資源✨ 最新活動 &amp; 免費下載👉 掃描影片裡的 QR Code</t>
+          <t>當你打開我的相簿📱</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>08/29/2025</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vLW3lKeD1Lw","https://www.youtube.com/watch?v=vLW3lKeD1Lw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
       </c>
       <c r="E100" s="2">
-        <v>4</v>
+        <v>364</v>
       </c>
       <c r="F100" s="2">
         <v>0</v>
@@ -4412,24 +4412,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>QB_An7T2_H0</t>
+          <t>vbRmUsUOG6A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🎒📚 開學季，樂樂家庭會員有專屬福利！👉 這次我們準備了「DIY 書包設計小活動」：✔️ 孩子能自己畫專屬書包</t>
+          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>08/29/2025</t>
+          <t>09/03/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QB_An7T2_H0","https://www.youtube.com/watch?v=QB_An7T2_H0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
       </c>
       <c r="E101" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F101" s="2">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5382,7 +5382,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5397,7 +5397,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24698</v>
+        <v>24472</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -460,7 +460,7 @@
         <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
       </c>
       <c r="C18" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2">
-        <v>18580</v>
+        <v>18694</v>
       </c>
       <c r="D27" s="2">
-        <v>344.1</v>
+        <v>339.9</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2">
-        <v>6118</v>
+        <v>5778</v>
       </c>
       <c r="D28" s="2">
-        <v>133</v>
+        <v>128.4</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E3" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,24 +823,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E4" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E5" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,24 +897,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E6" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -934,33 +934,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E7" s="2">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -971,33 +971,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E8" s="2">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1008,33 +1008,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E9" s="2">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,33 +1045,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E10" s="2">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.0064</v>
+        <v>0.0459</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E11" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0299</v>
+        <v>0.0133</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1119,33 +1119,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E12" s="2">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1156,24 +1156,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E13" s="2">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0476</v>
+        <v>0.0299</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E14" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,33 +1230,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E15" s="2">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,24 +1267,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E16" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,24 +1341,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E18" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1378,70 +1378,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E19" s="2">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="F19" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E20" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E21" s="2">
-        <v>92</v>
+        <v>576</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E22" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,24 +1526,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E23" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E24" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E25" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E26" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,64 +1674,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E27" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E28" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -1748,70 +1748,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E29" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E30" s="2">
-        <v>1115</v>
+        <v>216</v>
       </c>
       <c r="F30" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.0117</v>
+        <v>0.0046</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E31" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,33 +1859,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E32" s="2">
-        <v>978</v>
+        <v>1115</v>
       </c>
       <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2">
         <v>5</v>
       </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>0.0051</v>
+        <v>0.0117</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E33" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E34" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,24 +1970,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E35" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2007,24 +2007,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E36" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E37" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2074,31 +2074,31 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E38" s="2">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -2111,19 +2111,19 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E39" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,12 +2155,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2169,19 +2169,19 @@
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E40" s="2">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,12 +2192,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E41" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2229,12 +2229,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2243,19 +2243,19 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E42" s="2">
+        <v>101</v>
+      </c>
+      <c r="F42" s="2">
         <v>1</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,24 +2266,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E43" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2296,68 +2296,68 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E44" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E45" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -2370,40 +2370,40 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E46" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E47" s="2">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E48" s="2">
-        <v>1184</v>
+        <v>1109</v>
       </c>
       <c r="F48" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G48" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E49" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E50" s="2">
-        <v>403</v>
+        <v>1184</v>
       </c>
       <c r="F50" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G50" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,24 +2562,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E51" s="2">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2592,40 +2592,40 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E52" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F52" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,33 +2636,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E53" s="2">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,33 +2673,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E54" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F54" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,33 +2710,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E55" s="2">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,33 +2747,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E56" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F56" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,24 +2784,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E57" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2814,19 +2814,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E58" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -2851,19 +2851,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2872,130 +2872,130 @@
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E59" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E60" s="2">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="F60" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E61" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F61" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E62" s="2">
-        <v>333</v>
+        <v>696</v>
       </c>
       <c r="F62" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,24 +3006,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -3036,77 +3036,77 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E64" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E65" s="2">
-        <v>1177</v>
+        <v>2</v>
       </c>
       <c r="F65" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,24 +3117,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -3143,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0571</v>
+        <v>0.0513</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,33 +3154,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E67" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F67" s="2">
+        <v>3</v>
+      </c>
+      <c r="G67" s="2">
         <v>1</v>
       </c>
-      <c r="G67" s="2">
-        <v>0</v>
-      </c>
       <c r="H67" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,70 +3191,70 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E68" s="2">
-        <v>1317</v>
+        <v>35</v>
       </c>
       <c r="F68" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0114</v>
+        <v>0.0571</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E69" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,144 +3265,144 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E70" s="2">
-        <v>35</v>
+        <v>1317</v>
       </c>
       <c r="F70" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0571</v>
+        <v>0.0114</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E71" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F71" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E72" s="2">
-        <v>531</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0113</v>
+        <v>0.0556</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E73" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F73" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,33 +3413,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E74" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3450,24 +3450,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E75" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,33 +3487,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E76" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,107 +3524,107 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E77" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F77" s="2">
         <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E78" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E79" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F79" s="2">
         <v>1</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,24 +3635,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E80" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -3665,114 +3665,114 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E81" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F81" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E82" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F82" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E83" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F83" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,70 +3783,70 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E84" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F84" s="2">
         <v>10</v>
       </c>
-      <c r="F84" s="2">
-        <v>0</v>
-      </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E85" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F85" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,70 +3857,70 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E86" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E87" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F87" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,24 +3931,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E88" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -3957,44 +3957,44 @@
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E89" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E90" s="2">
-        <v>1074</v>
+        <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,24 +4042,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E91" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -4079,70 +4079,70 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E92" s="2">
-        <v>136</v>
+        <v>1074</v>
       </c>
       <c r="F92" s="2">
+        <v>13</v>
+      </c>
+      <c r="G92" s="2">
         <v>1</v>
       </c>
-      <c r="G92" s="2">
-        <v>0</v>
-      </c>
       <c r="H92" s="3">
-        <v>0.0074</v>
+        <v>0.013</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E93" s="2">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,33 +4153,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E94" s="2">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,33 +4190,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E95" s="2">
-        <v>947</v>
+        <v>217</v>
       </c>
       <c r="F95" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0095</v>
+        <v>0.0046</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,33 +4227,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E96" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,33 +4264,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E97" s="2">
-        <v>19</v>
+        <v>949</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,24 +4301,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1Vyb1Lt5UOU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>設定目標  🎯 setting goals～Stephanie</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E98" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.011</v>
+        <v>0.05</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,24 +4338,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>XPAxt3Tx2D8</t>
+          <t>NwXxciSquSU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
+          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
       </c>
       <c r="E99" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4375,33 +4375,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HDcdYMMnKjY</t>
+          <t>1Vyb1Lt5UOU</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>當你打開我的相簿📱</t>
+          <t>設定目標  🎯 setting goals～Stephanie</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HDcdYMMnKjY","https://www.youtube.com/watch?v=HDcdYMMnKjY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
       </c>
       <c r="E100" s="2">
-        <v>364</v>
+        <v>100</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,12 +4412,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>vbRmUsUOG6A</t>
+          <t>XPAxt3Tx2D8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>香港孩子直接閱讀識字🚄 提早一年學會1500個字～Sophie</t>
+          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vbRmUsUOG6A","https://www.youtube.com/watch?v=vbRmUsUOG6A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
       </c>
       <c r="E101" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F101" s="2">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5382,7 +5382,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5397,7 +5397,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24472</v>
+        <v>24411</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -440,7 +440,7 @@
         <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C17" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D17" s="2">
         <v>12</v>
@@ -500,7 +500,7 @@
         <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D20" s="2">
         <v>8</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2">
-        <v>18694</v>
+        <v>18722</v>
       </c>
       <c r="D27" s="2">
-        <v>339.9</v>
+        <v>334.3</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2">
-        <v>5778</v>
+        <v>5689</v>
       </c>
       <c r="D28" s="2">
-        <v>128.4</v>
+        <v>129.3</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E2" s="2">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,24 +786,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E3" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.04</v>
+        <v>0.0455</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,24 +823,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E4" s="2">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E5" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,24 +897,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E6" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -934,33 +934,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E7" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -971,24 +971,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E8" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1008,33 +1008,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E9" s="2">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,33 +1045,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E10" s="2">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E11" s="2">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1119,33 +1119,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E12" s="2">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.0064</v>
+        <v>0.0459</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1156,33 +1156,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E13" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0299</v>
+        <v>0.0133</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,33 +1193,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E14" s="2">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1230,24 +1230,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E15" s="2">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2">
         <v>2</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0476</v>
+        <v>0.0294</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,24 +1267,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E16" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E17" s="2">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,24 +1341,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E18" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E19" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E20" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
@@ -1452,70 +1452,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E21" s="2">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="F21" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E22" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,33 +1526,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E23" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E24" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,24 +1600,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E25" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E26" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E27" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E28" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,64 +1748,64 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E30" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -1822,70 +1822,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E31" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E32" s="2">
-        <v>1115</v>
+        <v>216</v>
       </c>
       <c r="F32" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0117</v>
+        <v>0.0046</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E33" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F33" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E34" s="2">
-        <v>978</v>
+        <v>1116</v>
       </c>
       <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="2">
         <v>5</v>
       </c>
-      <c r="G34" s="2">
-        <v>0</v>
-      </c>
       <c r="H34" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E35" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E36" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E37" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,24 +2081,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E38" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E39" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2148,31 +2148,31 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E40" s="2">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
@@ -2185,19 +2185,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E41" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2229,12 +2229,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2243,19 +2243,19 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E42" s="2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,12 +2266,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E43" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2303,12 +2303,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E44" s="2">
+        <v>101</v>
+      </c>
+      <c r="F44" s="2">
         <v>1</v>
       </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,24 +2340,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E45" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -2370,68 +2370,68 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E46" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E47" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2444,40 +2444,40 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E48" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F48" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E49" s="2">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E50" s="2">
-        <v>1184</v>
+        <v>1109</v>
       </c>
       <c r="F50" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G50" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,33 +2562,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E51" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,33 +2599,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E52" s="2">
-        <v>403</v>
+        <v>1185</v>
       </c>
       <c r="F52" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,24 +2636,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E53" s="2">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2666,40 +2666,40 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E54" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F54" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,33 +2710,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E55" s="2">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,33 +2747,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E56" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F56" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,33 +2784,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E57" s="2">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2821,33 +2821,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E58" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F58" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,24 +2858,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E59" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2888,19 +2888,19 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E60" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2925,19 +2925,19 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2946,130 +2946,130 @@
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E61" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F61" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E62" s="2">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E63" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E64" s="2">
-        <v>333</v>
+        <v>696</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,24 +3080,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E65" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -3110,77 +3110,77 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E66" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E67" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,24 +3191,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E68" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F68" s="2">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0571</v>
+        <v>0.0513</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,33 +3228,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E69" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F69" s="2">
+        <v>3</v>
+      </c>
+      <c r="G69" s="2">
         <v>1</v>
       </c>
-      <c r="G69" s="2">
-        <v>0</v>
-      </c>
       <c r="H69" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,70 +3265,70 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E70" s="2">
-        <v>1317</v>
+        <v>35</v>
       </c>
       <c r="F70" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0114</v>
+        <v>0.0571</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E71" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,144 +3339,144 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E72" s="2">
-        <v>36</v>
+        <v>1317</v>
       </c>
       <c r="F72" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0556</v>
+        <v>0.0114</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E73" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F73" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E74" s="2">
-        <v>531</v>
+        <v>37</v>
       </c>
       <c r="F74" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0113</v>
+        <v>0.0541</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E75" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,33 +3487,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E76" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,24 +3524,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E77" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F77" s="2">
         <v>1</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,33 +3561,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E78" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,107 +3598,107 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E79" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F79" s="2">
         <v>1</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E80" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E81" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E82" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -3739,114 +3739,114 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E83" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E84" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F84" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E85" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,70 +3857,70 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E86" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F86" s="2">
         <v>10</v>
       </c>
-      <c r="F86" s="2">
-        <v>0</v>
-      </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E87" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F87" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,70 +3931,70 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E88" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E89" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F89" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E90" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F90" s="2">
         <v>1</v>
@@ -4031,44 +4031,44 @@
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E91" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F91" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E92" s="2">
-        <v>1074</v>
+        <v>100</v>
       </c>
       <c r="F92" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,24 +4116,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E93" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F93" s="2">
         <v>0</v>
@@ -4153,70 +4153,70 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E94" s="2">
-        <v>136</v>
+        <v>1074</v>
       </c>
       <c r="F94" s="2">
+        <v>13</v>
+      </c>
+      <c r="G94" s="2">
         <v>1</v>
       </c>
-      <c r="G94" s="2">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
-        <v>0.0074</v>
+        <v>0.013</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E95" s="2">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,33 +4227,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E96" s="2">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="F96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,33 +4264,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E97" s="2">
-        <v>949</v>
+        <v>217</v>
       </c>
       <c r="F97" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0095</v>
+        <v>0.0046</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,33 +4301,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E98" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,33 +4338,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E99" s="2">
-        <v>19</v>
+        <v>949</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,24 +4375,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1Vyb1Lt5UOU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>設定目標  🎯 setting goals～Stephanie</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Vyb1Lt5UOU","https://www.youtube.com/watch?v=1Vyb1Lt5UOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E100" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F100" s="2">
         <v>1</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,24 +4412,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>XPAxt3Tx2D8</t>
+          <t>NwXxciSquSU</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>025｜【樂樂 Talk】小孩坐不住，還能學中文嗎？——給不想逼孩子的爸媽的語言解方｜S3E07</t>
+          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/03/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XPAxt3Tx2D8","https://www.youtube.com/watch?v=XPAxt3Tx2D8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
       </c>
       <c r="E101" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F101" s="2">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5397,7 +5397,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24411</v>
+        <v>24430</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2">
-        <v>18722</v>
+        <v>18756</v>
       </c>
       <c r="D27" s="2">
-        <v>334.3</v>
+        <v>329.1</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2">
-        <v>5689</v>
+        <v>5674</v>
       </c>
       <c r="D28" s="2">
-        <v>129.3</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E2" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,172 +786,172 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E3" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E4" s="2">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E5" s="2">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E6" s="2">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E7" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -964,31 +964,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E8" s="2">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1001,105 +1001,105 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E9" s="2">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E10" s="2">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E11" s="2">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1112,105 +1112,105 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E12" s="2">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="F12" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E13" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0133</v>
+        <v>0.0459</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E14" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1219,183 +1219,183 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.0064</v>
+        <v>0.0133</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E15" s="2">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0294</v>
+        <v>0.0064</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E16" s="2">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E17" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0465</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E18" s="2">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E19" s="2">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -1408,31 +1408,31 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E20" s="2">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
@@ -1445,114 +1445,114 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E21" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E22" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E23" s="2">
-        <v>577</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E24" s="2">
-        <v>40</v>
+        <v>577</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.025</v>
+        <v>0.0069</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E25" s="2">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E26" s="2">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0089</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E27" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,24 +1711,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E28" s="2">
-        <v>271</v>
+        <v>83</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E29" s="2">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,24 +1785,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E30" s="2">
-        <v>439</v>
+        <v>346</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.0046</v>
+        <v>0.0058</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,49 +1822,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E31" s="2">
-        <v>4</v>
+        <v>439</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1873,47 +1873,47 @@
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E32" s="2">
-        <v>216</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E33" s="2">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0036</v>
+        <v>0.0046</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E34" s="2">
-        <v>1116</v>
+        <v>278</v>
       </c>
       <c r="F34" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.0116</v>
+        <v>0.0036</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E35" s="2">
-        <v>700</v>
+        <v>1116</v>
       </c>
       <c r="F35" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G35" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0043</v>
+        <v>0.0116</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E36" s="2">
-        <v>978</v>
+        <v>700</v>
       </c>
       <c r="F36" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0051</v>
+        <v>0.0043</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,33 +2044,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E37" s="2">
-        <v>70</v>
+        <v>978</v>
       </c>
       <c r="F37" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E38" s="2">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E39" s="2">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,24 +2155,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E40" s="2">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
@@ -2192,24 +2192,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E41" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2222,19 +2222,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E42" s="2">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -2266,12 +2266,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E43" s="2">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2303,12 +2303,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E44" s="2">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="F44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,12 +2340,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2354,19 +2354,19 @@
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E45" s="2">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E46" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -2414,24 +2414,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E47" s="2">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2444,40 +2444,40 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E48" s="2">
-        <v>679</v>
+        <v>155</v>
       </c>
       <c r="F48" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,49 +2488,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E49" s="2">
-        <v>65</v>
+        <v>679</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2539,204 +2539,204 @@
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E50" s="2">
-        <v>1109</v>
+        <v>65</v>
       </c>
       <c r="F50" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E51" s="2">
-        <v>36</v>
+        <v>1109</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0278</v>
+        <v>0.0027</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E52" s="2">
-        <v>1185</v>
+        <v>37</v>
       </c>
       <c r="F52" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0127</v>
+        <v>0.027</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E53" s="2">
-        <v>13</v>
+        <v>1185</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G53" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="3">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E54" s="2">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E55" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="F55" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E56" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -2784,33 +2784,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E57" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2821,33 +2821,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E58" s="2">
-        <v>1026</v>
+        <v>105</v>
       </c>
       <c r="F58" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0068</v>
+        <v>0.0095</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,33 +2858,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E59" s="2">
-        <v>50</v>
+        <v>1026</v>
       </c>
       <c r="F59" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2895,24 +2895,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E60" s="2">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2932,12 +2932,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E61" s="2">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,19 +2962,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -3006,12 +3006,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3020,56 +3020,56 @@
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E63" s="2">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E64" s="2">
-        <v>696</v>
+        <v>1132</v>
       </c>
       <c r="F64" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0057</v>
+        <v>0.0062</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,61 +3080,61 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E65" s="2">
-        <v>15</v>
+        <v>696</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E66" s="2">
-        <v>333</v>
+        <v>15</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -3147,31 +3147,31 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E67" s="2">
-        <v>2</v>
+        <v>333</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -3191,181 +3191,181 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E68" s="2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E69" s="2">
-        <v>1178</v>
+        <v>39</v>
       </c>
       <c r="F69" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0034</v>
+        <v>0.0513</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E70" s="2">
-        <v>35</v>
+        <v>1178</v>
       </c>
       <c r="F70" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0571</v>
+        <v>0.0034</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E71" s="2">
-        <v>211</v>
+        <v>35</v>
       </c>
       <c r="F71" s="2">
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0047</v>
+        <v>0.0571</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E72" s="2">
-        <v>1317</v>
+        <v>211</v>
       </c>
       <c r="F72" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0114</v>
+        <v>0.0047</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,33 +3376,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E73" s="2">
-        <v>70</v>
+        <v>1317</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,61 +3413,61 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E74" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0541</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E75" s="2">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0127</v>
+        <v>0.0541</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,12 +3487,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3501,158 +3501,158 @@
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E76" s="2">
-        <v>531</v>
+        <v>158</v>
       </c>
       <c r="F76" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0113</v>
+        <v>0.0127</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E77" s="2">
-        <v>47</v>
+        <v>531</v>
       </c>
       <c r="F77" s="2">
+        <v>5</v>
+      </c>
+      <c r="G77" s="2">
         <v>1</v>
       </c>
-      <c r="G77" s="2">
-        <v>0</v>
-      </c>
       <c r="H77" s="3">
-        <v>0.0213</v>
+        <v>0.0113</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E78" s="2">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E79" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="F79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E80" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -3661,44 +3661,44 @@
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E81" s="2">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0294</v>
+        <v>0.04</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,107 +3709,107 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E82" s="2">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E83" s="2">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E84" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3820,70 +3820,70 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E85" s="2">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="F85" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E86" s="2">
-        <v>1830</v>
+        <v>96</v>
       </c>
       <c r="F86" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0055</v>
+        <v>0.0312</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,33 +3894,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E87" s="2">
-        <v>6</v>
+        <v>1830</v>
       </c>
       <c r="F87" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,12 +3931,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E88" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -3961,77 +3961,77 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E89" s="2">
-        <v>924</v>
+        <v>10</v>
       </c>
       <c r="F89" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E90" s="2">
-        <v>27</v>
+        <v>924</v>
       </c>
       <c r="F90" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.037</v>
+        <v>0.0184</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,33 +4042,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E91" s="2">
-        <v>323</v>
+        <v>27</v>
       </c>
       <c r="F91" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0093</v>
+        <v>0.037</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,49 +4079,49 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E92" s="2">
-        <v>100</v>
+        <v>323</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.01</v>
+        <v>0.0093</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4130,130 +4130,130 @@
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E93" s="2">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E94" s="2">
-        <v>1074</v>
+        <v>9</v>
       </c>
       <c r="F94" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E95" s="2">
-        <v>15</v>
+        <v>1074</v>
       </c>
       <c r="F95" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E96" s="2">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,24 +4264,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>W3yWoHlXbQ8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>蛋炒飯串起與家人的回憶</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/20/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
       </c>
       <c r="E97" s="2">
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="F97" s="2">
         <v>1</v>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0046</v>
+        <v>0.0074</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,33 +4301,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>o63PbJSSIME</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>教孩子不能用我們小時候的方法</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
       </c>
       <c r="E98" s="2">
-        <v>10</v>
+        <v>217</v>
       </c>
       <c r="F98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,33 +4338,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>oXFtZxpw3TM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/17/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
       </c>
       <c r="E99" s="2">
-        <v>949</v>
+        <v>10</v>
       </c>
       <c r="F99" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,33 +4375,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>8dYZrgBXARI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/11/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
       </c>
       <c r="E100" s="2">
-        <v>20</v>
+        <v>949</v>
       </c>
       <c r="F100" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.05</v>
+        <v>0.0095</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,33 +4412,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NwXxciSquSU</t>
+          <t>gKFvpuSTAnI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>為什麼孩子能在故事中 自然地把文字圖像和經驗連起來</t>
+          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NwXxciSquSU","https://www.youtube.com/watch?v=NwXxciSquSU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
       </c>
       <c r="E101" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5382,7 +5382,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5397,7 +5397,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24430</v>
+        <v>23700</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2">
-        <v>18756</v>
+        <v>18764</v>
       </c>
       <c r="D27" s="2">
-        <v>329.1</v>
+        <v>318</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2">
-        <v>5674</v>
+        <v>4936</v>
       </c>
       <c r="D28" s="2">
-        <v>132</v>
+        <v>120.4</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E2" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,24 +786,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E3" s="2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -823,33 +823,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E4" s="2">
-        <v>23</v>
+        <v>534</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0435</v>
+        <v>0.0075</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -860,24 +860,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>父親節兒歌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E5" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -890,40 +890,40 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E6" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,24 +934,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E7" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -971,21 +971,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E8" s="2">
         <v>24</v>
@@ -1001,142 +1001,142 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E9" s="2">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E10" s="2">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E11" s="2">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E12" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1149,179 +1149,179 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E13" s="2">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="F13" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E14" s="2">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E15" s="2">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0064</v>
+        <v>0.0588</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E16" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0.0294</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E17" s="2">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -1334,262 +1334,262 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E18" s="2">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.0465</v>
+        <v>0.0459</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E19" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>0.0132</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E20" s="2">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E21" s="2">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E22" s="2">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E23" s="2">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E24" s="2">
-        <v>577</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,61 +1600,61 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E25" s="2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E26" s="2">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -1674,61 +1674,61 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E27" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0089</v>
+        <v>0.0476</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E28" s="2">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E29" s="2">
-        <v>271</v>
+        <v>577</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E30" s="2">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.0058</v>
+        <v>0.025</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E31" s="2">
-        <v>439</v>
+        <v>92</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,70 +1859,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E32" s="2">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E33" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E34" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E35" s="2">
-        <v>1116</v>
+        <v>346</v>
       </c>
       <c r="F35" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G35" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0116</v>
+        <v>0.0058</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E36" s="2">
-        <v>700</v>
+        <v>439</v>
       </c>
       <c r="F36" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0043</v>
+        <v>0.0046</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,70 +2044,70 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E37" s="2">
-        <v>978</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E38" s="2">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,33 +2118,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E39" s="2">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E40" s="2">
-        <v>127</v>
+        <v>1116</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G40" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,33 +2192,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E41" s="2">
-        <v>91</v>
+        <v>700</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,61 +2229,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E42" s="2">
-        <v>80</v>
+        <v>978</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E43" s="2">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -2296,31 +2296,31 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E44" s="2">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -2333,68 +2333,68 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E45" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E46" s="2">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -2407,19 +2407,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E47" s="2">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2451,24 +2451,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E48" s="2">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -2481,77 +2481,77 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E49" s="2">
-        <v>679</v>
+        <v>50</v>
       </c>
       <c r="F49" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E50" s="2">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,70 +2562,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E51" s="2">
-        <v>1109</v>
+        <v>13</v>
       </c>
       <c r="F51" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E52" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,33 +2636,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E53" s="2">
-        <v>1185</v>
+        <v>155</v>
       </c>
       <c r="F53" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,107 +2673,107 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E54" s="2">
-        <v>14</v>
+        <v>679</v>
       </c>
       <c r="F54" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E55" s="2">
-        <v>403</v>
+        <v>65</v>
       </c>
       <c r="F55" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E56" s="2">
-        <v>78</v>
+        <v>1109</v>
       </c>
       <c r="F56" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,70 +2784,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E57" s="2">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E58" s="2">
-        <v>105</v>
+        <v>1185</v>
       </c>
       <c r="F58" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G58" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0095</v>
+        <v>0.0127</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,70 +2858,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E59" s="2">
-        <v>1026</v>
+        <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E60" s="2">
-        <v>50</v>
+        <v>403</v>
       </c>
       <c r="F60" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2932,24 +2932,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E61" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2969,24 +2969,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E62" s="2">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -2999,68 +2999,68 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E63" s="2">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E64" s="2">
-        <v>1132</v>
+        <v>1026</v>
       </c>
       <c r="F64" s="2">
         <v>7</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0062</v>
+        <v>0.0068</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,33 +3080,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E65" s="2">
-        <v>696</v>
+        <v>50</v>
       </c>
       <c r="F65" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,24 +3117,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E66" s="2">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -3147,31 +3147,31 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E67" s="2">
-        <v>333</v>
+        <v>3</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -3184,31 +3184,31 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E68" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -3221,77 +3221,77 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E69" s="2">
-        <v>39</v>
+        <v>1132</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0513</v>
+        <v>0.0062</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E70" s="2">
-        <v>1178</v>
+        <v>696</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0034</v>
+        <v>0.0057</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,33 +3302,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E71" s="2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0571</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E72" s="2">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="F72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0047</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,33 +3376,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E73" s="2">
-        <v>1317</v>
+        <v>2</v>
       </c>
       <c r="F73" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,107 +3413,107 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E74" s="2">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
+        <v>0.0513</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E75" s="2">
-        <v>37</v>
+        <v>1178</v>
       </c>
       <c r="F75" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0541</v>
+        <v>0.0034</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E76" s="2">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="F76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0127</v>
+        <v>0.0571</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,33 +3524,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E77" s="2">
-        <v>531</v>
+        <v>211</v>
       </c>
       <c r="F77" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0113</v>
+        <v>0.0047</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,61 +3561,61 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E78" s="2">
-        <v>47</v>
+        <v>1317</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0213</v>
+        <v>0.0114</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E79" s="2">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -3635,33 +3635,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E80" s="2">
         <v>37</v>
       </c>
       <c r="F80" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.027</v>
+        <v>0.0541</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3672,70 +3672,70 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E81" s="2">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="F81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.04</v>
+        <v>0.0127</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E82" s="2">
-        <v>68</v>
+        <v>531</v>
       </c>
       <c r="F82" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0294</v>
+        <v>0.0113</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3746,33 +3746,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E83" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,33 +3783,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E84" s="2">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3820,135 +3820,135 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E85" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E86" s="2">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F86" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0312</v>
+        <v>0.04</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E87" s="2">
-        <v>1830</v>
+        <v>68</v>
       </c>
       <c r="F87" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0055</v>
+        <v>0.0294</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E88" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -3968,33 +3968,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E89" s="2">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,70 +4005,70 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E90" s="2">
-        <v>924</v>
+        <v>45</v>
       </c>
       <c r="F90" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E91" s="2">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="F91" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.037</v>
+        <v>0.0312</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E92" s="2">
-        <v>323</v>
+        <v>1830</v>
       </c>
       <c r="F92" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.0093</v>
+        <v>0.0055</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,61 +4116,61 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E93" s="2">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E94" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -4183,77 +4183,77 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E95" s="2">
-        <v>1074</v>
+        <v>924</v>
       </c>
       <c r="F95" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.013</v>
+        <v>0.0184</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E96" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,33 +4264,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>W3yWoHlXbQ8</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>蛋炒飯串起與家人的回憶</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/20/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=W3yWoHlXbQ8","https://www.youtube.com/watch?v=W3yWoHlXbQ8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E97" s="2">
-        <v>136</v>
+        <v>323</v>
       </c>
       <c r="F97" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0074</v>
+        <v>0.0093</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,24 +4301,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>o63PbJSSIME</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>教孩子不能用我們小時候的方法</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=o63PbJSSIME","https://www.youtube.com/watch?v=o63PbJSSIME")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E98" s="2">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -4327,35 +4327,35 @@
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.0046</v>
+        <v>0.01</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>oXFtZxpw3TM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>027｜【樂樂 Talk】另一半不會中文，怎麼辦？——讓全家一起參與孩子中文學習的實戰方法｜S3E09</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/17/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oXFtZxpw3TM","https://www.youtube.com/watch?v=oXFtZxpw3TM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E99" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4375,70 +4375,70 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8dYZrgBXARI</t>
+          <t>1Yp-hUO3SpA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>✈️ 都移民了為什麼還要教小孩中文 🧳 🏠</t>
+          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/11/2025</t>
+          <t>09/25/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8dYZrgBXARI","https://www.youtube.com/watch?v=8dYZrgBXARI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
       </c>
       <c r="E100" s="2">
-        <v>949</v>
+        <v>1074</v>
       </c>
       <c r="F100" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0095</v>
+        <v>0.013</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>gKFvpuSTAnI</t>
+          <t>hLqDU4hlBCM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>026｜【樂樂 Talk】海外陪孩子學中文最常見的兩個誤區——注音和識字量，你掉進去了嗎？｜S3E08</t>
+          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gKFvpuSTAnI","https://www.youtube.com/watch?v=gKFvpuSTAnI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
       </c>
       <c r="E101" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -177,7 +177,7 @@
         <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
         <v>Public comments from exported videos</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>23700</v>
+        <v>24610</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -243,7 +243,7 @@
         <v>Public comments total</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v/>
@@ -265,7 +265,7 @@
         <v>Videos with comments</v>
       </c>
       <c r="B9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2">
         <v/>
@@ -417,19 +417,19 @@
         <v>2</v>
       </c>
       <c r="B16" s="2">
-        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
+        <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1317</v>
+        <v>1780</v>
       </c>
       <c r="D16" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
     </row>
     <row r="17">
@@ -437,19 +437,19 @@
         <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>力玄華語對我的家族其實是外來語 #shorts</v>
+        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
       </c>
       <c r="C17" s="2">
-        <v>1185</v>
+        <v>1317</v>
       </c>
       <c r="D17" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
     </row>
     <row r="18">
@@ -457,19 +457,19 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
+        <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C18" s="2">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="D18" s="2">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2">
         <v>3</v>
       </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
       <c r="F18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
     </row>
     <row r="19">
@@ -477,19 +477,19 @@
         <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
+        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
       </c>
       <c r="C19" s="2">
-        <v>1132</v>
+        <v>1178</v>
       </c>
       <c r="D19" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
     </row>
     <row r="20">
@@ -497,19 +497,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>我的母語是什麼 #shorts</v>
+        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="D20" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
     </row>
     <row r="21">
@@ -517,19 +517,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="2">
-        <v>如何在海外創造必須用中文的環境 #shorts</v>
+        <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
     </row>
     <row r="22">
@@ -537,19 +537,19 @@
         <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</v>
+        <v>如何在海外創造必須用中文的環境 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1074</v>
+        <v>1109</v>
       </c>
       <c r="D22" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
     </row>
     <row r="23">
@@ -644,10 +644,10 @@
         <v>59</v>
       </c>
       <c r="C27" s="2">
-        <v>18764</v>
+        <v>17734</v>
       </c>
       <c r="D27" s="2">
-        <v>318</v>
+        <v>300.6</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -666,10 +666,10 @@
         <v>41</v>
       </c>
       <c r="C28" s="2">
-        <v>4936</v>
+        <v>6876</v>
       </c>
       <c r="D28" s="2">
-        <v>120.4</v>
+        <v>167.7</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,98 +786,98 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E3" s="2">
+        <v>682</v>
+      </c>
+      <c r="F3" s="2">
         <v>3</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E4" s="2">
-        <v>534</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>父親節兒歌</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E5" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -890,40 +890,40 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E6" s="2">
-        <v>32</v>
+        <v>1780</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,24 +934,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E7" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -964,31 +964,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E8" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1001,68 +1001,68 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E9" s="2">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E10" s="2">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1082,24 +1082,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E11" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0385</v>
+        <v>0.0357</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1156,33 +1156,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E13" s="2">
         <v>26</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E14" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,33 +1230,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E15" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E16" s="2">
         <v>64</v>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E17" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E18" s="2">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E19" s="2">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,33 +1415,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E20" s="2">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0064</v>
+        <v>0.0455</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E21" s="2">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0294</v>
+        <v>0.0132</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E22" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,24 +1526,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E23" s="2">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2">
         <v>2</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0465</v>
+        <v>0.0294</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,24 +1563,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E24" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E25" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,24 +1637,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E26" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E27" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,24 +1711,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E28" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -1748,70 +1748,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E29" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="F29" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E30" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E31" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,33 +1859,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E32" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,24 +1896,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E33" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E34" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E35" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F35" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E36" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,64 +2044,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E37" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F37" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E38" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -2118,70 +2118,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E39" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E40" s="2">
-        <v>1116</v>
+        <v>216</v>
       </c>
       <c r="F40" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0116</v>
+        <v>0.0046</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,33 +2192,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E41" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F41" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,33 +2229,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E42" s="2">
-        <v>978</v>
+        <v>1116</v>
       </c>
       <c r="F42" s="2">
+        <v>8</v>
+      </c>
+      <c r="G42" s="2">
         <v>5</v>
       </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E43" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,33 +2303,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E44" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F44" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,24 +2340,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E45" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -2377,24 +2377,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E46" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -2414,24 +2414,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E47" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2444,31 +2444,31 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E48" s="2">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -2481,19 +2481,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E49" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -2525,12 +2525,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2539,19 +2539,19 @@
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E50" s="2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,12 +2562,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E51" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2599,12 +2599,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2613,19 +2613,19 @@
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E52" s="2">
+        <v>101</v>
+      </c>
+      <c r="F52" s="2">
         <v>1</v>
       </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,24 +2636,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E53" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2666,68 +2666,68 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E54" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F54" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E55" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2740,40 +2740,40 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E56" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F56" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,33 +2784,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E57" s="2">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2821,33 +2821,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E58" s="2">
-        <v>1185</v>
+        <v>1109</v>
       </c>
       <c r="F58" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G58" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,33 +2858,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E59" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2895,33 +2895,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E60" s="2">
-        <v>403</v>
+        <v>1185</v>
       </c>
       <c r="F60" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G60" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2932,24 +2932,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E61" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,40 +2962,40 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E62" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F62" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,33 +3006,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E63" s="2">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,33 +3043,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E64" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F64" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,33 +3080,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E65" s="2">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,33 +3117,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E66" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F66" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,24 +3154,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E67" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -3184,19 +3184,19 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E68" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -3221,19 +3221,19 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3242,130 +3242,130 @@
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E69" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F69" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E70" s="2">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E71" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F71" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E72" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F72" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,24 +3376,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E73" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -3406,77 +3406,77 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E74" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E75" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F75" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,24 +3487,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E76" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0571</v>
+        <v>0.0513</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,33 +3524,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E77" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F77" s="2">
+        <v>3</v>
+      </c>
+      <c r="G77" s="2">
         <v>1</v>
       </c>
-      <c r="G77" s="2">
-        <v>0</v>
-      </c>
       <c r="H77" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,70 +3561,70 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E78" s="2">
-        <v>1317</v>
+        <v>36</v>
       </c>
       <c r="F78" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0114</v>
+        <v>0.0556</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E79" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,144 +3635,144 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E80" s="2">
-        <v>37</v>
+        <v>1317</v>
       </c>
       <c r="F80" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0541</v>
+        <v>0.0114</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E81" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F81" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E82" s="2">
-        <v>531</v>
+        <v>39</v>
       </c>
       <c r="F82" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0113</v>
+        <v>0.0513</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E83" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,33 +3783,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E84" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F84" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3820,24 +3820,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E85" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,33 +3857,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E86" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,107 +3894,107 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E87" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F87" s="2">
         <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E88" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E89" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F89" s="2">
         <v>1</v>
       </c>
       <c r="G89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E90" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -4035,114 +4035,114 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E91" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F91" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E92" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F92" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E93" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,70 +4153,70 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E94" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F94" s="2">
         <v>10</v>
       </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E95" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F95" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,70 +4227,70 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E96" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E97" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F97" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,24 +4301,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E98" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -4327,44 +4327,44 @@
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E99" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,33 +4375,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1Yp-hUO3SpA</t>
+          <t>accuuAQqCiY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
+          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/25/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
       </c>
       <c r="E100" s="2">
-        <v>1074</v>
+        <v>100</v>
       </c>
       <c r="F100" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,24 +4412,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>hLqDU4hlBCM</t>
+          <t>7LCi7ktmZXk</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>028｜【樂樂 Talk】我不夠努力？——打破自我否定，用一杯珍奶的心態開始陪孩子學中文｜S3E10</t>
+          <t>原來孩子放棄中文的真正原因是....</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>09/27/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=hLqDU4hlBCM","https://www.youtube.com/watch?v=hLqDU4hlBCM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
       </c>
       <c r="E101" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F101" s="2">
         <v>0</v>
@@ -5266,61 +5266,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1Yp-hUO3SpA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>聽起來不可思議但太多家庭都遇到一樣的問題 #shorts</t>
-        </is>
-      </c>
-      <c r="C16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1Yp-hUO3SpA","https://www.youtube.com/watch?v=1Yp-hUO3SpA")</f>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>@心自己嚇自己</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>09/26/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>？那所以我可以重讀幼兒園了！</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>學習/共讀</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>未分類</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K15"/>
 </worksheet>
 </file>
 

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>24610</v>
+        <v>27730</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -397,19 +397,19 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>想要月餅活動紙留言GROUP</v>
+        <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
       </c>
       <c r="C15" s="2">
-        <v>1830</v>
+        <v>3763</v>
       </c>
       <c r="D15" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
       </c>
       <c r="F15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
     </row>
     <row r="16">
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1780</v>
+        <v>1841</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -437,19 +437,19 @@
         <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
+        <v>想要月餅活動紙留言GROUP</v>
       </c>
       <c r="C17" s="2">
-        <v>1317</v>
+        <v>1830</v>
       </c>
       <c r="D17" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
     </row>
     <row r="18">
@@ -457,19 +457,19 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>力玄華語對我的家族其實是外來語 #shorts</v>
+        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
       </c>
       <c r="C18" s="2">
-        <v>1185</v>
+        <v>1317</v>
       </c>
       <c r="D18" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
     </row>
     <row r="19">
@@ -477,19 +477,19 @@
         <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
+        <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C19" s="2">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="D19" s="2">
+        <v>12</v>
+      </c>
+      <c r="E19" s="2">
         <v>3</v>
       </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
       <c r="F19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
     </row>
     <row r="20">
@@ -497,19 +497,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
+        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1132</v>
+        <v>1178</v>
       </c>
       <c r="D20" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
     </row>
     <row r="21">
@@ -517,19 +517,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="2">
-        <v>我的母語是什麼 #shorts</v>
+        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="D21" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
     </row>
     <row r="22">
@@ -537,19 +537,19 @@
         <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>如何在海外創造必須用中文的環境 #shorts</v>
+        <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
     </row>
     <row r="23">
@@ -557,19 +557,19 @@
         <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
+        <v>如何在海外創造必須用中文的環境 #shorts</v>
       </c>
       <c r="C23" s="2">
-        <v>1026</v>
+        <v>1109</v>
       </c>
       <c r="D23" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
     </row>
     <row r="24">
@@ -577,19 +577,19 @@
         <v>10</v>
       </c>
       <c r="B24" s="2">
-        <v>真正重要的不是字數而是他能不能讀懂故事 #shorts</v>
+        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
       </c>
       <c r="C24" s="2">
-        <v>978</v>
+        <v>1026</v>
       </c>
       <c r="D24" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
     </row>
     <row r="25">
@@ -644,10 +644,10 @@
         <v>59</v>
       </c>
       <c r="C27" s="2">
-        <v>17734</v>
+        <v>17691</v>
       </c>
       <c r="D27" s="2">
-        <v>300.6</v>
+        <v>299.8</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -666,10 +666,10 @@
         <v>41</v>
       </c>
       <c r="C28" s="2">
-        <v>6876</v>
+        <v>10039</v>
       </c>
       <c r="D28" s="2">
-        <v>167.7</v>
+        <v>244.9</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E2" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E3" s="2">
-        <v>682</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0044</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,24 +823,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E4" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,98 +860,98 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E5" s="2">
-        <v>7</v>
+        <v>3763</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E6" s="2">
-        <v>1780</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E7" s="2">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -964,40 +964,40 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E8" s="2">
-        <v>33</v>
+        <v>1841</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1008,24 +1008,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E9" s="2">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1038,31 +1038,31 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E10" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1075,31 +1075,31 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E11" s="2">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
@@ -1108,35 +1108,35 @@
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0357</v>
+        <v>0.0233</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E12" s="2">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1156,24 +1156,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E13" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0385</v>
+        <v>0.0357</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,33 +1230,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E15" s="2">
         <v>27</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,24 +1267,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E16" s="2">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E17" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E18" s="2">
         <v>65</v>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E19" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,33 +1415,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E20" s="2">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="F20" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E21" s="2">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E22" s="2">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0063</v>
+        <v>0.0455</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,33 +1526,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E23" s="2">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0294</v>
+        <v>0.0132</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E24" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,24 +1600,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E25" s="2">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.0465</v>
+        <v>0.0294</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,24 +1637,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E26" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E27" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,24 +1711,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E28" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E29" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,24 +1785,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E30" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -1822,70 +1822,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E31" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="F31" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E32" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E33" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E34" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,24 +1970,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E35" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E36" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,33 +2044,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E37" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E38" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,64 +2118,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E39" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E40" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
@@ -2192,70 +2192,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E41" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E42" s="2">
-        <v>1116</v>
+        <v>216</v>
       </c>
       <c r="F42" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0116</v>
+        <v>0.0046</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E43" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F43" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,33 +2303,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E44" s="2">
-        <v>978</v>
+        <v>1116</v>
       </c>
       <c r="F44" s="2">
+        <v>8</v>
+      </c>
+      <c r="G44" s="2">
         <v>5</v>
       </c>
-      <c r="G44" s="2">
-        <v>0</v>
-      </c>
       <c r="H44" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E45" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,33 +2377,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E46" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F46" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,24 +2414,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E47" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -2451,24 +2451,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E48" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -2488,24 +2488,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E49" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -2518,31 +2518,31 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E50" s="2">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -2555,19 +2555,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E51" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2599,12 +2599,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2613,19 +2613,19 @@
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E52" s="2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,12 +2636,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E53" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2673,12 +2673,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2687,19 +2687,19 @@
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E54" s="2">
+        <v>101</v>
+      </c>
+      <c r="F54" s="2">
         <v>1</v>
       </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,24 +2710,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E55" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2740,68 +2740,68 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E56" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E57" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2814,40 +2814,40 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E58" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,33 +2858,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E59" s="2">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2895,33 +2895,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E60" s="2">
-        <v>1185</v>
+        <v>1109</v>
       </c>
       <c r="F60" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G60" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2932,33 +2932,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E61" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2969,33 +2969,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E62" s="2">
-        <v>403</v>
+        <v>1185</v>
       </c>
       <c r="F62" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G62" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0099</v>
+        <v>0.0127</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,24 +3006,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E63" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -3036,40 +3036,40 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E64" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,33 +3080,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E65" s="2">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,33 +3117,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E66" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F66" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,33 +3154,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E67" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,33 +3191,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E68" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,24 +3228,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E69" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -3258,19 +3258,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E70" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -3295,19 +3295,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3316,130 +3316,130 @@
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E71" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F71" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E72" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F72" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E73" s="2">
-        <v>15</v>
+        <v>1132</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E74" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3450,24 +3450,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -3480,77 +3480,77 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E76" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E77" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,24 +3561,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E78" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F78" s="2">
         <v>1</v>
@@ -3587,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0556</v>
+        <v>0.0513</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,33 +3598,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E79" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F79" s="2">
+        <v>3</v>
+      </c>
+      <c r="G79" s="2">
         <v>1</v>
       </c>
-      <c r="G79" s="2">
-        <v>0</v>
-      </c>
       <c r="H79" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,70 +3635,70 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E80" s="2">
-        <v>1317</v>
+        <v>36</v>
       </c>
       <c r="F80" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0114</v>
+        <v>0.0556</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E81" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,144 +3709,144 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E82" s="2">
-        <v>39</v>
+        <v>1317</v>
       </c>
       <c r="F82" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0513</v>
+        <v>0.0114</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E83" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E84" s="2">
-        <v>531</v>
+        <v>41</v>
       </c>
       <c r="F84" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0113</v>
+        <v>0.0488</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E85" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F85" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,33 +3857,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E86" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F86" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,24 +3894,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E87" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F87" s="2">
         <v>1</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,33 +3931,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E88" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,107 +3968,107 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E89" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F89" s="2">
         <v>1</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E90" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E91" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F91" s="2">
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,24 +4079,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E92" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -4109,114 +4109,114 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E93" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F93" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E94" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F94" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E95" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F95" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,70 +4227,70 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E96" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F96" s="2">
         <v>10</v>
       </c>
-      <c r="F96" s="2">
-        <v>0</v>
-      </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E97" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F97" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,70 +4301,70 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E98" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E99" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F99" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,24 +4375,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>accuuAQqCiY</t>
+          <t>L2Ub9RDXP3Y</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>萬聖節 10 日共讀挑戰開跑 #shorts</t>
+          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>10/01/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=accuuAQqCiY","https://www.youtube.com/watch?v=accuuAQqCiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
       </c>
       <c r="E100" s="2">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F100" s="2">
         <v>1</v>
@@ -4401,44 +4401,44 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7LCi7ktmZXk</t>
+          <t>gfA8thtxR0k</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....</t>
+          <t>你準備好孩子長期的中文計劃了嗎</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/27/2025</t>
+          <t>09/30/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7LCi7ktmZXk","https://www.youtube.com/watch?v=7LCi7ktmZXk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
       </c>
       <c r="E101" s="2">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5329,7 +5329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B4" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -177,7 +177,7 @@
         <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>Public comments from exported videos</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>27730</v>
+        <v>31329</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -400,10 +400,10 @@
         <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
       </c>
       <c r="C15" s="2">
-        <v>3763</v>
+        <v>6769</v>
       </c>
       <c r="D15" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1841</v>
+        <v>1860</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -480,7 +480,7 @@
         <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C19" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D19" s="2">
         <v>12</v>
@@ -560,7 +560,7 @@
         <v>如何在海外創造必須用中文的環境 #shorts</v>
       </c>
       <c r="C23" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
-        <v>17691</v>
+        <v>18589</v>
       </c>
       <c r="D27" s="2">
-        <v>299.8</v>
+        <v>304.7</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2">
-        <v>10039</v>
+        <v>12740</v>
       </c>
       <c r="D28" s="2">
-        <v>244.9</v>
+        <v>326.7</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E2" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,61 +786,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E3" s="2">
+        <v>818</v>
+      </c>
+      <c r="F3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E4" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E5" s="2">
-        <v>3763</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,24 +897,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E6" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -934,98 +934,98 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E7" s="2">
-        <v>12</v>
+        <v>6769</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E8" s="2">
-        <v>1841</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E9" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1038,40 +1038,40 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E10" s="2">
-        <v>37</v>
+        <v>1860</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1082,61 +1082,61 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E11" s="2">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.0233</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E12" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1149,31 +1149,31 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E13" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1182,35 +1182,35 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0357</v>
+        <v>0.0222</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E14" s="2">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,24 +1230,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E15" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.037</v>
+        <v>0.0357</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,24 +1267,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,33 +1304,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,24 +1341,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E18" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E19" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E20" s="2">
         <v>65</v>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E21" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E22" s="2">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,33 +1526,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E23" s="2">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E24" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0063</v>
+        <v>0.0442</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E25" s="2">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.0294</v>
+        <v>0.013</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E26" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,24 +1674,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E27" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F27" s="2">
         <v>2</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0465</v>
+        <v>0.029</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,24 +1711,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E28" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E29" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,24 +1785,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E30" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E31" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,24 +1859,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E32" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -1896,70 +1896,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E33" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E34" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E35" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E36" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E37" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E38" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,33 +2118,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E39" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E40" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,64 +2192,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E41" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E42" s="2">
-        <v>216</v>
+        <v>439</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -2266,70 +2266,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E43" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E44" s="2">
-        <v>1116</v>
+        <v>216</v>
       </c>
       <c r="F44" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0116</v>
+        <v>0.0046</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E45" s="2">
-        <v>700</v>
+        <v>278</v>
       </c>
       <c r="F45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,33 +2377,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E46" s="2">
-        <v>978</v>
+        <v>1116</v>
       </c>
       <c r="F46" s="2">
+        <v>8</v>
+      </c>
+      <c r="G46" s="2">
         <v>5</v>
       </c>
-      <c r="G46" s="2">
-        <v>0</v>
-      </c>
       <c r="H46" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E47" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F47" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E48" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F48" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,24 +2488,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E49" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -2525,24 +2525,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E50" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -2562,24 +2562,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E51" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2592,31 +2592,31 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E52" s="2">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -2629,19 +2629,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E53" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2673,12 +2673,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2687,19 +2687,19 @@
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E54" s="2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,12 +2710,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E55" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2747,12 +2747,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E56" s="2">
+        <v>101</v>
+      </c>
+      <c r="F56" s="2">
         <v>1</v>
       </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,24 +2784,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E57" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2814,68 +2814,68 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E58" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E59" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2888,40 +2888,40 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E60" s="2">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="F60" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2932,33 +2932,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E61" s="2">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2969,33 +2969,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E62" s="2">
-        <v>1185</v>
+        <v>1111</v>
       </c>
       <c r="F62" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,33 +3006,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E63" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,33 +3043,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E64" s="2">
-        <v>403</v>
+        <v>1186</v>
       </c>
       <c r="F64" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G64" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0099</v>
+        <v>0.0126</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,24 +3080,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E65" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -3110,40 +3110,40 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E66" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F66" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,33 +3154,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E67" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,33 +3191,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E68" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F68" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,33 +3228,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E69" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,33 +3265,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E70" s="2">
-        <v>197</v>
+        <v>1026</v>
       </c>
       <c r="F70" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,24 +3302,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E71" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -3332,19 +3332,19 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E72" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -3369,19 +3369,19 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3390,130 +3390,130 @@
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E73" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F73" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E74" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E75" s="2">
-        <v>16</v>
+        <v>1132</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E76" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,24 +3524,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E77" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -3554,77 +3554,77 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E78" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E79" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F79" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,24 +3635,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E80" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F80" s="2">
         <v>1</v>
@@ -3661,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0556</v>
+        <v>0.0513</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3672,33 +3672,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E81" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F81" s="2">
+        <v>3</v>
+      </c>
+      <c r="G81" s="2">
         <v>1</v>
       </c>
-      <c r="G81" s="2">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,70 +3709,70 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E82" s="2">
-        <v>1317</v>
+        <v>37</v>
       </c>
       <c r="F82" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E83" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,144 +3783,144 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E84" s="2">
-        <v>41</v>
+        <v>1317</v>
       </c>
       <c r="F84" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0488</v>
+        <v>0.0114</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E85" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F85" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E86" s="2">
-        <v>531</v>
+        <v>42</v>
       </c>
       <c r="F86" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0113</v>
+        <v>0.0476</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E87" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F87" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,33 +3931,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E88" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F88" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="3">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,24 +3968,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E89" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F89" s="2">
         <v>1</v>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E90" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,107 +4042,107 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E91" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F91" s="2">
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E92" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E93" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F93" s="2">
         <v>1</v>
       </c>
       <c r="G93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,24 +4153,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E94" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -4183,114 +4183,114 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E95" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F95" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E96" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F96" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E97" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,70 +4301,70 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E98" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F98" s="2">
         <v>10</v>
       </c>
-      <c r="F98" s="2">
-        <v>0</v>
-      </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E99" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F99" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,70 +4375,70 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L2Ub9RDXP3Y</t>
+          <t>k-CNvcbt7SA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>029｜【樂樂 Talk】孩子現在只願意說英文——從今天開始，永遠不嫌晚的改變方法｜S3E11</t>
+          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/01/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L2Ub9RDXP3Y","https://www.youtube.com/watch?v=L2Ub9RDXP3Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
       </c>
       <c r="E100" s="2">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>gfA8thtxR0k</t>
+          <t>BGxO2XSkydo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>你準備好孩子長期的中文計劃了嗎</t>
+          <t>最有效的方法反而是免費的</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09/30/2025</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gfA8thtxR0k","https://www.youtube.com/watch?v=gfA8thtxR0k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
       </c>
       <c r="E101" s="2">
-        <v>323</v>
+        <v>924</v>
       </c>
       <c r="F101" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.0093</v>
+        <v>0.0184</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>@yenyanchen2752</t>
+          <t>@fet092</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>❤❤❤</t>
+          <t>台語就是眾多華語中的一支。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@fet092</t>
+          <t>@peter90004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>台語就是眾多華語中的一支。</t>
+          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>@peter90004</t>
+          <t>@frankzheng5494</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F4" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
+          <t>原來就是說閩南語方言啦！</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>@frankzheng5494</t>
+          <t>@arielcc5397</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>原來就是說閩南語方言啦！</t>
+          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>@arielcc5397</t>
+          <t>@kcma-k9l</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
+          <t>台独</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>政治/爭議</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4785,40 +4785,40 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>@kcma-k9l</t>
+          <t>@debc8406</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>台独</t>
+          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>海外環境, 家庭語言</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>@debc8406</t>
+          <t>@suika_hachikai</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4867,31 +4867,31 @@
         </is>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
+          <t>部分正確。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>政治/爭議</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>海外環境, 家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@suika_hachikai</t>
+          <t>@貓星人-c6i</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4920,64 +4920,64 @@
         </is>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>部分正確。</t>
+          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>@貓星人-c6i</t>
+          <t>@zhenfan2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
+          <t>最後兒子亂入是共讀最好示範😅</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4987,42 +4987,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>學習/共讀</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>@zhenfan2</t>
+          <t>@Lennonrx8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="F11" s="2">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>最後兒子亂入是共讀最好示範😅</t>
+          <t>华文才难学啊，英文太简单了</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5040,37 +5040,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>@Lennonrx8</t>
+          <t>@QCASo01PegatronUuUsss</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>华文才难学啊，英文太简单了</t>
+          <t>❤❤❤❤❤❤❤</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5110,25 +5110,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@QCASo01PegatronUuUsss</t>
+          <t>@annieyang6601</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11/16/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="F13" s="2">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>❤❤❤❤❤❤❤</t>
+          <t>我想共學</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>學習/共讀</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5156,23 +5156,23 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>我想共學</t>
+          <t>了解整套</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -5209,65 +5209,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8__o_r_dr4M</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
-        </is>
-      </c>
-      <c r="C15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>@annieyang6601</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>10/30/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>了解整套</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>未分類</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
           <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
 </worksheet>
 </file>
 
@@ -5314,7 +5261,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -5329,7 +5276,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B4" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -177,7 +177,7 @@
         <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
         <v>Public comments from exported videos</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>31329</v>
+        <v>31936</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -400,10 +400,10 @@
         <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
       </c>
       <c r="C15" s="2">
-        <v>6769</v>
+        <v>8177</v>
       </c>
       <c r="D15" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1860</v>
+        <v>1878</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -540,7 +540,7 @@
         <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D22" s="2">
         <v>8</v>
@@ -580,7 +580,7 @@
         <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
       </c>
       <c r="C24" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D24" s="2">
         <v>7</v>
@@ -644,10 +644,10 @@
         <v>61</v>
       </c>
       <c r="C27" s="2">
-        <v>18589</v>
+        <v>18641</v>
       </c>
       <c r="D27" s="2">
-        <v>304.7</v>
+        <v>305.6</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -666,10 +666,10 @@
         <v>39</v>
       </c>
       <c r="C28" s="2">
-        <v>12740</v>
+        <v>13295</v>
       </c>
       <c r="D28" s="2">
-        <v>326.7</v>
+        <v>340.9</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ob31JAy9EO0</t>
+          <t>4zqbHokYRiA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
+          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
       </c>
       <c r="E2" s="2">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,61 +786,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7ra5Zka3C2Y</t>
+          <t>pStoU9mSTYg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
+          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
       </c>
       <c r="E3" s="2">
-        <v>818</v>
+        <v>32</v>
       </c>
       <c r="F3" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0061</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E4" s="2">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -860,61 +860,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E5" s="2">
-        <v>8</v>
+        <v>834</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E6" s="2">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -934,33 +934,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E7" s="2">
-        <v>6769</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -971,24 +971,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E8" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1008,98 +1008,98 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E9" s="2">
-        <v>18</v>
+        <v>8177</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E10" s="2">
-        <v>1860</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E11" s="2">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1112,40 +1112,40 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E12" s="2">
-        <v>38</v>
+        <v>1878</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1156,61 +1156,61 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E13" s="2">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0222</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E14" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E15" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1256,35 +1256,35 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0357</v>
+        <v>0.0217</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E16" s="2">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1304,24 +1304,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E17" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.037</v>
+        <v>0.0357</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,24 +1341,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1378,33 +1378,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E19" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E20" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
@@ -1452,33 +1452,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E21" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,24 +1489,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E22" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
@@ -1526,33 +1526,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E23" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E24" s="2">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,33 +1600,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E25" s="2">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E26" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0063</v>
+        <v>0.0442</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E27" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E28" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,24 +1748,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E29" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0465</v>
+        <v>0.029</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,24 +1785,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E30" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E31" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,24 +1859,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E32" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E33" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,24 +1933,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E34" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -1970,70 +1970,70 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E35" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="F35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E36" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,33 +2044,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E37" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F37" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E38" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E39" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E40" s="2">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,33 +2192,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E41" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,33 +2229,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E42" s="2">
-        <v>439</v>
+        <v>271</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0046</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,70 +2266,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E43" s="2">
-        <v>4</v>
+        <v>346</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E44" s="2">
-        <v>216</v>
+        <v>440</v>
       </c>
       <c r="F44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0046</v>
+        <v>0.0045</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,70 +2340,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E45" s="2">
-        <v>278</v>
+        <v>7</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E46" s="2">
-        <v>1116</v>
+        <v>217</v>
       </c>
       <c r="F46" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0116</v>
+        <v>0.0092</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E47" s="2">
-        <v>700</v>
+        <v>279</v>
       </c>
       <c r="F47" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E48" s="2">
-        <v>978</v>
+        <v>1119</v>
       </c>
       <c r="F48" s="2">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2">
         <v>5</v>
       </c>
-      <c r="G48" s="2">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E49" s="2">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E50" s="2">
-        <v>180</v>
+        <v>978</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,24 +2562,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E51" s="2">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -2599,24 +2599,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E52" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -2636,24 +2636,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E53" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2666,31 +2666,31 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E54" s="2">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -2703,19 +2703,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E55" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2747,12 +2747,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E56" s="2">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,12 +2784,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E57" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2821,12 +2821,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E58" s="2">
+        <v>101</v>
+      </c>
+      <c r="F58" s="2">
         <v>1</v>
       </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,24 +2858,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E59" s="2">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2888,68 +2888,68 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E60" s="2">
-        <v>679</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
       </c>
       <c r="H60" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E61" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,40 +2962,40 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E62" s="2">
-        <v>1111</v>
+        <v>679</v>
       </c>
       <c r="F62" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,33 +3006,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E63" s="2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,33 +3043,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E64" s="2">
-        <v>1186</v>
+        <v>1111</v>
       </c>
       <c r="F64" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0126</v>
+        <v>0.0027</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3080,33 +3080,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E65" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,33 +3117,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E66" s="2">
-        <v>403</v>
+        <v>1186</v>
       </c>
       <c r="F66" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G66" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0099</v>
+        <v>0.0126</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,24 +3154,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E67" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -3184,40 +3184,40 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E68" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,33 +3228,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E69" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,33 +3265,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E70" s="2">
-        <v>1026</v>
+        <v>116</v>
       </c>
       <c r="F70" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,33 +3302,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E71" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E72" s="2">
-        <v>197</v>
+        <v>1027</v>
       </c>
       <c r="F72" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,24 +3376,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E73" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -3406,19 +3406,19 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E74" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -3443,19 +3443,19 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3464,130 +3464,130 @@
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E75" s="2">
-        <v>1132</v>
+        <v>3</v>
       </c>
       <c r="F75" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E76" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E77" s="2">
-        <v>17</v>
+        <v>1132</v>
       </c>
       <c r="F77" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E78" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,24 +3598,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E79" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -3628,77 +3628,77 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E80" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E81" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F81" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E82" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F82" s="2">
         <v>1</v>
@@ -3735,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0541</v>
+        <v>0.0513</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3746,33 +3746,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E83" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F83" s="2">
+        <v>3</v>
+      </c>
+      <c r="G83" s="2">
         <v>1</v>
       </c>
-      <c r="G83" s="2">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,70 +3783,70 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E84" s="2">
-        <v>1317</v>
+        <v>37</v>
       </c>
       <c r="F84" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E85" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,144 +3857,144 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E86" s="2">
-        <v>42</v>
+        <v>1317</v>
       </c>
       <c r="F86" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0476</v>
+        <v>0.0114</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E87" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F87" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E88" s="2">
-        <v>531</v>
+        <v>43</v>
       </c>
       <c r="F88" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.0094</v>
+        <v>0.0465</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E89" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E90" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,24 +4042,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E91" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F91" s="2">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4079,33 +4079,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E92" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,107 +4116,107 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E93" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F93" s="2">
         <v>1</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E94" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E95" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,24 +4227,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E96" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -4257,114 +4257,114 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E97" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F97" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E98" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F98" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E99" s="2">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,70 +4375,70 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>k-CNvcbt7SA</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>中秋月圓人團圓一家烤肉萬家香  再過幾天就是中秋節了10月6日是不是已經開始聞到哪家飄來的烤肉香了呢在台灣有個非常特別的中秋節習俗家家戶戶都會在院子烤肉邊賞月邊烤肉家人朋友 #shorts</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-CNvcbt7SA","https://www.youtube.com/watch?v=k-CNvcbt7SA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E100" s="2">
+        <v>1830</v>
+      </c>
+      <c r="F100" s="2">
         <v>10</v>
       </c>
-      <c r="F100" s="2">
-        <v>0</v>
-      </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BGxO2XSkydo</t>
+          <t>KNS-WNSempE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>最有效的方法反而是免費的</t>
+          <t>月圓人團圓</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BGxO2XSkydo","https://www.youtube.com/watch?v=BGxO2XSkydo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
       </c>
       <c r="E101" s="2">
-        <v>924</v>
+        <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>@fet092</t>
+          <t>@yenyanchen2752</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="F2" s="2">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台語就是眾多華語中的一支。</t>
+          <t>❤❤❤</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@peter90004</t>
+          <t>@fet092</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
+          <t>台語就是眾多華語中的一支。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>@frankzheng5494</t>
+          <t>@peter90004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="F4" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>原來就是說閩南語方言啦！</t>
+          <t>蔣介石的母語是浙江寧波語，也不是北京話，國語就是要讓大家好溝通而已</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>@arielcc5397</t>
+          <t>@frankzheng5494</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
+          <t>原來就是說閩南語方言啦！</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>@kcma-k9l</t>
+          <t>@arielcc5397</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台独</t>
+          <t>笑屎。。。往上一代去追尋？？所以追到了什麼啦？？？？？</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>政治/爭議</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4785,40 +4785,40 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>@debc8406</t>
+          <t>@kcma-k9l</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
+          <t>台独</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>海外環境, 家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>@suika_hachikai</t>
+          <t>@debc8406</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4867,31 +4867,31 @@
         </is>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>部分正確。</t>
+          <t>你所謂的‘’台語‘’，其實是‘閩南語’，最近3，40年才在台灣改名的，為了滿足去中國化的意識形態。所以，你沒必要擔心它失傳，講閩南語的最大族群不在台灣。您也不必覺得講‘’中文‘’等於‘親中，必須把‘中文‘改稱為‘’華語’’。英語到了澳洲，紐西蘭，和美國同樣是英語，沒有變成澳洲話，紐西蘭話，美國話。美國人講英語並不影響國家的獨立性。但是，當一個國家為了政治因素而要切斷文化的根時，應該考慮那麼我們還剩什麼？在我們推行台灣版的 cancel Culture 時，它其實是一場台灣版的文化大革命。它將給後代帶來的是文化真空，和滿腦子的意識形態。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>政治/爭議</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>海外環境, 家庭語言</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>低衝突回覆：感謝分享，拉回家庭語言與親子連結，不辯政治立場。</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@貓星人-c6i</t>
+          <t>@suika_hachikai</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4920,64 +4920,64 @@
         </is>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
+          <t>部分正確。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>家庭語言</t>
+          <t>未分類</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>@zhenfan2</t>
+          <t>@貓星人-c6i</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>最後兒子亂入是共讀最好示範😅</t>
+          <t>我的小孩學會講話的第一句就是台語，他是學會台語上幼稚園以後才開始學華語 他現在17歲台語很OK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4987,42 +4987,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>家庭語言</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+          <t>可回覆：肯定每個家庭的語言選擇，邀請分享家中使用語言的故事。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>@Lennonrx8</t>
+          <t>@zhenfan2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11/16/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="F11" s="2">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>华文才难学啊，英文太简单了</t>
+          <t>最後兒子亂入是共讀最好示範😅</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5040,37 +5040,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>學習/共讀</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>孩子只說英文</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>@QCASo01PegatronUuUsss</t>
+          <t>@Lennonrx8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>❤❤❤❤❤❤❤</t>
+          <t>华文才难学啊，英文太简单了</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>未分類</t>
+          <t>孩子只說英文</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5110,25 +5110,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@annieyang6601</t>
+          <t>@QCASo01PegatronUuUsss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="F13" s="2">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>我想共學</t>
+          <t>❤❤❤❤❤❤❤</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>學習/共讀</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5156,65 +5156,118 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>iOcGa4QDSbs</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+        </is>
+      </c>
+      <c r="C14" s="4">
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>@annieyang6601</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>我想共學</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>學習/共讀</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>未分類</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>可回覆：接住家長經驗，補一句每天一點點、陪伴比完美重要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>8__o_r_dr4M</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
-      <c r="C14" s="4">
+      <c r="C15" s="4">
         <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>@annieyang6601</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>10/30/2025</t>
         </is>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>了解整套</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>未分類</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
 </worksheet>
 </file>
 
@@ -5276,7 +5329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5291,7 +5344,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>31936</v>
+        <v>33258</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -400,10 +400,10 @@
         <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
       </c>
       <c r="C15" s="2">
-        <v>8177</v>
+        <v>9220</v>
       </c>
       <c r="D15" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1878</v>
+        <v>1888</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -520,7 +520,7 @@
         <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D21" s="2">
         <v>7</v>
@@ -540,7 +540,7 @@
         <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D22" s="2">
         <v>8</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>18641</v>
+        <v>18907</v>
       </c>
       <c r="D27" s="2">
-        <v>305.6</v>
+        <v>305</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="2">
-        <v>13295</v>
+        <v>14351</v>
       </c>
       <c r="D28" s="2">
-        <v>340.9</v>
+        <v>377.7</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4zqbHokYRiA</t>
+          <t>3NtAzWC9dVQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
+          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
       </c>
       <c r="E2" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,24 +786,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pStoU9mSTYg</t>
+          <t>4zqbHokYRiA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
+          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
       </c>
       <c r="E3" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -816,31 +816,31 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ob31JAy9EO0</t>
+          <t>pStoU9mSTYg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
+          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
       </c>
       <c r="E4" s="2">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -853,19 +853,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7ra5Zka3C2Y</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E5" s="2">
-        <v>834</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,33 +897,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E6" s="2">
-        <v>43</v>
+        <v>835</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,24 +934,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E7" s="2">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -964,31 +964,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E8" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1001,93 +1001,93 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E9" s="2">
-        <v>8177</v>
+        <v>32</v>
       </c>
       <c r="F9" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E10" s="2">
-        <v>14</v>
+        <v>9220</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E11" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1119,49 +1119,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E12" s="2">
-        <v>1878</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E13" s="2">
-        <v>89</v>
+        <v>1888</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E14" s="2">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1230,70 +1230,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E15" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E16" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1304,172 +1304,172 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E17" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0357</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E18" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>0.0357</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E19" s="2">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E20" s="2">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E21" s="2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -1482,31 +1482,31 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E22" s="2">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
@@ -1519,105 +1519,105 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E23" s="2">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E24" s="2">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E25" s="2">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -1630,105 +1630,105 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E26" s="2">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="F26" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E27" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.013</v>
+        <v>0.0442</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E28" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
@@ -1737,183 +1737,183 @@
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.0063</v>
+        <v>0.013</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E29" s="2">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.029</v>
+        <v>0.0063</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E30" s="2">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E31" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0465</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E32" s="2">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E33" s="2">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1926,31 +1926,31 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E34" s="2">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -1963,114 +1963,114 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E35" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E36" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E37" s="2">
-        <v>577</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="3">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E38" s="2">
-        <v>40</v>
+        <v>577</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.025</v>
+        <v>0.0069</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,33 +2118,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E39" s="2">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E40" s="2">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0089</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,33 +2192,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E41" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,24 +2229,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E42" s="2">
-        <v>271</v>
+        <v>85</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E43" s="2">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,24 +2303,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E44" s="2">
-        <v>440</v>
+        <v>348</v>
       </c>
       <c r="F44" s="2">
         <v>2</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0045</v>
+        <v>0.0057</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,49 +2340,49 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E45" s="2">
-        <v>7</v>
+        <v>441</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2391,56 +2391,56 @@
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E46" s="2">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0092</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E47" s="2">
-        <v>279</v>
+        <v>218</v>
       </c>
       <c r="F47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0036</v>
+        <v>0.0092</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E48" s="2">
-        <v>1119</v>
+        <v>280</v>
       </c>
       <c r="F48" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0116</v>
+        <v>0.0036</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E49" s="2">
-        <v>700</v>
+        <v>1120</v>
       </c>
       <c r="F49" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G49" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0043</v>
+        <v>0.0116</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E50" s="2">
-        <v>978</v>
+        <v>702</v>
       </c>
       <c r="F50" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0051</v>
+        <v>0.0043</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,33 +2562,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E51" s="2">
-        <v>70</v>
+        <v>979</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,24 +2599,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E52" s="2">
-        <v>180</v>
+        <v>71</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -2636,24 +2636,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E53" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -2673,24 +2673,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E54" s="2">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -2710,24 +2710,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E55" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2740,19 +2740,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E56" s="2">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -2784,12 +2784,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E57" s="2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2821,12 +2821,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E58" s="2">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2858,12 +2858,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E59" s="2">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="F59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2895,12 +2895,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E60" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2932,24 +2932,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E61" s="2">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,40 +2962,40 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E62" s="2">
-        <v>679</v>
+        <v>155</v>
       </c>
       <c r="F62" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3006,49 +3006,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E63" s="2">
-        <v>65</v>
+        <v>679</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3057,204 +3057,204 @@
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E64" s="2">
-        <v>1111</v>
+        <v>65</v>
       </c>
       <c r="F64" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E65" s="2">
-        <v>38</v>
+        <v>1111</v>
       </c>
       <c r="F65" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0263</v>
+        <v>0.0027</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E66" s="2">
-        <v>1186</v>
+        <v>38</v>
       </c>
       <c r="F66" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0126</v>
+        <v>0.0263</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E67" s="2">
-        <v>14</v>
+        <v>1186</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G67" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H67" s="3">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E68" s="2">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="F68" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E69" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,24 +3265,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E70" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -3302,33 +3302,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E71" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E72" s="2">
-        <v>1027</v>
+        <v>107</v>
       </c>
       <c r="F72" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0068</v>
+        <v>0.0093</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,33 +3376,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E73" s="2">
-        <v>50</v>
+        <v>1027</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,24 +3413,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E74" s="2">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -3450,12 +3450,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E75" s="2">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -3480,19 +3480,19 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E76" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -3524,12 +3524,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3538,56 +3538,56 @@
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E77" s="2">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E78" s="2">
-        <v>697</v>
+        <v>1134</v>
       </c>
       <c r="F78" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0057</v>
+        <v>0.0062</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,61 +3598,61 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E79" s="2">
-        <v>17</v>
+        <v>697</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E80" s="2">
-        <v>333</v>
+        <v>17</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -3665,31 +3665,31 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E81" s="2">
-        <v>2</v>
+        <v>333</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -3709,181 +3709,181 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E82" s="2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E83" s="2">
-        <v>1178</v>
+        <v>39</v>
       </c>
       <c r="F83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0034</v>
+        <v>0.0513</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E84" s="2">
-        <v>37</v>
+        <v>1178</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0541</v>
+        <v>0.0034</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E85" s="2">
-        <v>211</v>
+        <v>37</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
       </c>
       <c r="G85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0047</v>
+        <v>0.0541</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E86" s="2">
-        <v>1317</v>
+        <v>211</v>
       </c>
       <c r="F86" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0114</v>
+        <v>0.0047</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,33 +3894,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E87" s="2">
-        <v>70</v>
+        <v>1317</v>
       </c>
       <c r="F87" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,61 +3931,61 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E88" s="2">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F88" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.0465</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E89" s="2">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="F89" s="2">
         <v>2</v>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0127</v>
+        <v>0.0455</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,12 +4005,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4019,158 +4019,158 @@
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E90" s="2">
-        <v>531</v>
+        <v>158</v>
       </c>
       <c r="F90" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.0094</v>
+        <v>0.0127</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E91" s="2">
-        <v>47</v>
+        <v>531</v>
       </c>
       <c r="F91" s="2">
+        <v>4</v>
+      </c>
+      <c r="G91" s="2">
         <v>1</v>
       </c>
-      <c r="G91" s="2">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
-        <v>0.0213</v>
+        <v>0.0094</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E92" s="2">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>0.0213</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E93" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E94" s="2">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -4179,44 +4179,44 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E95" s="2">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0294</v>
+        <v>0.04</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,107 +4227,107 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E96" s="2">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="F96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E97" s="2">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E98" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,70 +4338,70 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E99" s="2">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="F99" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>jI0oXaLYHlw</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/07/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
       </c>
       <c r="E100" s="2">
-        <v>1830</v>
+        <v>96</v>
       </c>
       <c r="F100" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0055</v>
+        <v>0.0312</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,33 +4412,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KNS-WNSempE</t>
+          <t>0iC4fAn_-fM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>月圓人團圓</t>
+          <t>想要月餅活動紙留言GROUP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>10/05/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=KNS-WNSempE","https://www.youtube.com/watch?v=KNS-WNSempE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
       </c>
       <c r="E101" s="2">
-        <v>6</v>
+        <v>1830</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>33258</v>
+        <v>32057</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -400,10 +400,10 @@
         <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
       </c>
       <c r="C15" s="2">
-        <v>9220</v>
+        <v>9785</v>
       </c>
       <c r="D15" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1888</v>
+        <v>1892</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -437,19 +437,19 @@
         <v>3</v>
       </c>
       <c r="B17" s="2">
-        <v>想要月餅活動紙留言GROUP</v>
+        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
       </c>
       <c r="C17" s="2">
-        <v>1830</v>
+        <v>1317</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
     </row>
     <row r="18">
@@ -457,19 +457,19 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</v>
+        <v>力玄華語對我的家族其實是外來語 #shorts</v>
       </c>
       <c r="C18" s="2">
-        <v>1317</v>
+        <v>1186</v>
       </c>
       <c r="D18" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
     </row>
     <row r="19">
@@ -477,19 +477,19 @@
         <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>力玄華語對我的家族其實是外來語 #shorts</v>
+        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
       </c>
       <c r="C19" s="2">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="D19" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
     </row>
     <row r="20">
@@ -497,19 +497,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</v>
+        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
       </c>
       <c r="C20" s="2">
-        <v>1178</v>
+        <v>1134</v>
       </c>
       <c r="D20" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
     </row>
     <row r="21">
@@ -517,19 +517,19 @@
         <v>7</v>
       </c>
       <c r="B21" s="2">
-        <v>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</v>
+        <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="D21" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
     </row>
     <row r="22">
@@ -537,19 +537,19 @@
         <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>我的母語是什麼 #shorts</v>
+        <v>如何在海外創造必須用中文的環境 #shorts</v>
       </c>
       <c r="C22" s="2">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="D22" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
     </row>
     <row r="23">
@@ -557,19 +557,19 @@
         <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>如何在海外創造必須用中文的環境 #shorts</v>
+        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
       </c>
       <c r="C23" s="2">
-        <v>1111</v>
+        <v>1027</v>
       </c>
       <c r="D23" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
     </row>
     <row r="24">
@@ -577,19 +577,19 @@
         <v>10</v>
       </c>
       <c r="B24" s="2">
-        <v>沒有一個更好的老師因為父母就是最好的老師  #shorts</v>
+        <v>真正重要的不是字數而是他能不能讀懂故事 #shorts</v>
       </c>
       <c r="C24" s="2">
-        <v>1027</v>
+        <v>979</v>
       </c>
       <c r="D24" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
     </row>
     <row r="25">
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2">
-        <v>18907</v>
+        <v>19037</v>
       </c>
       <c r="D27" s="2">
-        <v>305</v>
+        <v>302.2</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="2">
-        <v>14351</v>
+        <v>13020</v>
       </c>
       <c r="D28" s="2">
-        <v>377.7</v>
+        <v>351.9</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,33 +749,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3NtAzWC9dVQ</t>
+          <t>81z7sy7UCoU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
+          <t>困難不在外面，而在心裡 ❤️ 一旦決定了，每個問題都有解方 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07/25/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=81z7sy7UCoU","https://www.youtube.com/watch?v=81z7sy7UCoU")</f>
       </c>
       <c r="E2" s="2">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="3">
-        <v>0</v>
+        <v>0.0079</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -786,21 +786,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4zqbHokYRiA</t>
+          <t>tBhdEUDbAmw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
+          <t>057｜【樂樂 Talk】孩子有自我修正的能力——大量聽讀如何讓洋腔洋調悄悄消失｜S3E20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tBhdEUDbAmw","https://www.youtube.com/watch?v=tBhdEUDbAmw")</f>
       </c>
       <c r="E3" s="2">
         <v>23</v>
@@ -816,31 +816,31 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pStoU9mSTYg</t>
+          <t>3NtAzWC9dVQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
+          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
       </c>
       <c r="E4" s="2">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -853,31 +853,31 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ob31JAy9EO0</t>
+          <t>4zqbHokYRiA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
+          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
       </c>
       <c r="E5" s="2">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -897,61 +897,61 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7ra5Zka3C2Y</t>
+          <t>pStoU9mSTYg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
+          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
       </c>
       <c r="E6" s="2">
-        <v>835</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E7" s="2">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -971,61 +971,61 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E8" s="2">
-        <v>10</v>
+        <v>836</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E9" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1045,33 +1045,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E10" s="2">
-        <v>9220</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1082,24 +1082,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E11" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1119,98 +1119,98 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E12" s="2">
-        <v>19</v>
+        <v>9785</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E13" s="2">
-        <v>1888</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E14" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1223,40 +1223,40 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E15" s="2">
-        <v>38</v>
+        <v>1892</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1267,61 +1267,61 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E16" s="2">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E17" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -1334,31 +1334,31 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E18" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -1367,35 +1367,35 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.0357</v>
+        <v>0.0217</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E19" s="2">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -1415,24 +1415,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E20" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.037</v>
+        <v>0.0357</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1452,24 +1452,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -1489,33 +1489,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E22" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,24 +1526,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E23" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E24" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,24 +1600,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E25" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E26" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,33 +1674,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E27" s="2">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F27" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E28" s="2">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E29" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0063</v>
+        <v>0.0442</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E30" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E31" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,24 +1859,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E32" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0465</v>
+        <v>0.029</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,24 +1896,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E33" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E34" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,24 +1970,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E35" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E36" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E37" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,70 +2081,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E38" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="F38" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.0069</v>
+        <v>0.0476</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E39" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E40" s="2">
-        <v>92</v>
+        <v>577</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,33 +2192,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E41" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,24 +2229,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E42" s="2">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E43" s="2">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,33 +2303,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E44" s="2">
-        <v>348</v>
+        <v>85</v>
       </c>
       <c r="F44" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E45" s="2">
-        <v>441</v>
+        <v>272</v>
       </c>
       <c r="F45" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,61 +2377,61 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E46" s="2">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="F46" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E47" s="2">
-        <v>218</v>
+        <v>441</v>
       </c>
       <c r="F47" s="2">
         <v>2</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0092</v>
+        <v>0.0045</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,70 +2451,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E48" s="2">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E49" s="2">
-        <v>1120</v>
+        <v>218</v>
       </c>
       <c r="F49" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0116</v>
+        <v>0.0092</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,33 +2525,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E50" s="2">
-        <v>702</v>
+        <v>280</v>
       </c>
       <c r="F50" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2562,33 +2562,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E51" s="2">
-        <v>979</v>
+        <v>1120</v>
       </c>
       <c r="F51" s="2">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2">
         <v>5</v>
       </c>
-      <c r="G51" s="2">
-        <v>0</v>
-      </c>
       <c r="H51" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,33 +2599,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E52" s="2">
-        <v>71</v>
+        <v>702</v>
       </c>
       <c r="F52" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,33 +2636,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E53" s="2">
-        <v>181</v>
+        <v>979</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,24 +2673,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E54" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -2710,24 +2710,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E55" s="2">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -2747,24 +2747,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E56" s="2">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -2777,31 +2777,31 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E57" s="2">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2814,19 +2814,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E58" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -2858,12 +2858,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E59" s="2">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="F59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2895,12 +2895,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E60" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2932,12 +2932,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2946,19 +2946,19 @@
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E61" s="2">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="F61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2969,24 +2969,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E62" s="2">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -2999,68 +2999,68 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E63" s="2">
-        <v>679</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E64" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -3073,40 +3073,40 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E65" s="2">
-        <v>1111</v>
+        <v>679</v>
       </c>
       <c r="F65" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,33 +3117,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E66" s="2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3154,33 +3154,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E67" s="2">
-        <v>1186</v>
+        <v>1111</v>
       </c>
       <c r="F67" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G67" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0126</v>
+        <v>0.0027</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,33 +3191,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E68" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,33 +3228,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E69" s="2">
-        <v>403</v>
+        <v>1186</v>
       </c>
       <c r="F69" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G69" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0099</v>
+        <v>0.0126</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,24 +3265,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E70" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -3295,40 +3295,40 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E71" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F71" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E72" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,33 +3376,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E73" s="2">
-        <v>1027</v>
+        <v>116</v>
       </c>
       <c r="F73" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,33 +3413,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E74" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3450,33 +3450,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E75" s="2">
-        <v>197</v>
+        <v>1027</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,24 +3487,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E76" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -3517,19 +3517,19 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E77" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -3554,19 +3554,19 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3575,130 +3575,130 @@
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E78" s="2">
-        <v>1134</v>
+        <v>3</v>
       </c>
       <c r="F78" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E79" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F79" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E80" s="2">
-        <v>17</v>
+        <v>1134</v>
       </c>
       <c r="F80" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E81" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E82" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -3739,77 +3739,77 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E83" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E84" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F84" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3820,24 +3820,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E85" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0541</v>
+        <v>0.0513</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,33 +3857,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E86" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F86" s="2">
+        <v>3</v>
+      </c>
+      <c r="G86" s="2">
         <v>1</v>
       </c>
-      <c r="G86" s="2">
-        <v>0</v>
-      </c>
       <c r="H86" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,70 +3894,70 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E87" s="2">
-        <v>1317</v>
+        <v>37</v>
       </c>
       <c r="F87" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E88" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,144 +3968,144 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E89" s="2">
-        <v>44</v>
+        <v>1317</v>
       </c>
       <c r="F89" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0455</v>
+        <v>0.0114</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E90" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F90" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E91" s="2">
-        <v>531</v>
+        <v>45</v>
       </c>
       <c r="F91" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0094</v>
+        <v>0.0444</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E92" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,33 +4116,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E93" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4153,24 +4153,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E94" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F94" s="2">
         <v>1</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,33 +4190,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E95" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,107 +4227,107 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E96" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E97" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E98" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
       </c>
       <c r="G98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,24 +4338,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E99" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
@@ -4368,81 +4368,81 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>jI0oXaLYHlw</t>
+          <t>6pWGpIUBSBs</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>030｜【樂樂 Talk】指讀指到母子離心？——厚厚私塾 Iris 談每個孩子都有自己的中文學習節奏（上）｜S1E11</t>
+          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/07/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=jI0oXaLYHlw","https://www.youtube.com/watch?v=jI0oXaLYHlw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
       </c>
       <c r="E100" s="2">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="F100" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0iC4fAn_-fM</t>
+          <t>5eDsf75XtOg</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>想要月餅活動紙留言GROUP</t>
+          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10/05/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0iC4fAn_-fM","https://www.youtube.com/watch?v=0iC4fAn_-fM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
       </c>
       <c r="E101" s="2">
-        <v>1830</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5344,7 +5344,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>32057</v>
+        <v>32730</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -221,7 +221,7 @@
         <v>Public likes total</v>
       </c>
       <c r="B7" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2">
         <v/>
@@ -287,7 +287,7 @@
         <v>Shorts count</v>
       </c>
       <c r="B10" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v/>
@@ -309,7 +309,7 @@
         <v>Long-form count</v>
       </c>
       <c r="B11" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2">
         <v/>
@@ -397,13 +397,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>和樂樂一起唱讀｜媽媽媽媽在哪裡</v>
+        <v>和樂樂一起唱讀｜媽媽媽媽在哪裡?</v>
       </c>
       <c r="C15" s="2">
-        <v>9785</v>
+        <v>10099</v>
       </c>
       <c r="D15" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2">
         <v>0</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1892</v>
+        <v>1899</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -641,13 +641,13 @@
         <v>Shorts</v>
       </c>
       <c r="B27" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>19037</v>
+        <v>18960</v>
       </c>
       <c r="D27" s="2">
-        <v>302.2</v>
+        <v>305.8</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -663,13 +663,13 @@
         <v>Long-form</v>
       </c>
       <c r="B28" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="2">
-        <v>13020</v>
+        <v>13770</v>
       </c>
       <c r="D28" s="2">
-        <v>351.9</v>
+        <v>362.4</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,33 +749,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>81z7sy7UCoU</t>
+          <t>vlS7Rmbj20s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>困難不在外面，而在心裡 ❤️ 一旦決定了，每個問題都有解方 #shorts</t>
+          <t>Emma 在家裡沒有中文環境，自己也不會中文，卻陪孩子讀完樂樂紅、黃、綠書 300 本！ #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=81z7sy7UCoU","https://www.youtube.com/watch?v=81z7sy7UCoU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vlS7Rmbj20s","https://www.youtube.com/watch?v=vlS7Rmbj20s")</f>
       </c>
       <c r="E2" s="2">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.0079</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tBhdEUDbAmw</t>
+          <t>goe-UOeBrOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>057｜【樂樂 Talk】孩子有自我修正的能力——大量聽讀如何讓洋腔洋調悄悄消失｜S3E20</t>
+          <t>和樂樂一起唱讀｜顏色朋友歌</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07/28/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tBhdEUDbAmw","https://www.youtube.com/watch?v=tBhdEUDbAmw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=goe-UOeBrOU","https://www.youtube.com/watch?v=goe-UOeBrOU")</f>
       </c>
       <c r="E3" s="2">
-        <v>23</v>
+        <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>0.0052</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,33 +823,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3NtAzWC9dVQ</t>
+          <t>81z7sy7UCoU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
+          <t>困難不在外面，而在心裡 ❤️ 一旦決定了，每個問題都有解方 #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07/25/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=81z7sy7UCoU","https://www.youtube.com/watch?v=81z7sy7UCoU")</f>
       </c>
       <c r="E4" s="2">
-        <v>241</v>
+        <v>128</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -860,24 +860,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4zqbHokYRiA</t>
+          <t>tBhdEUDbAmw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
+          <t>057｜【樂樂 Talk】孩子有自我修正的能力——大量聽讀如何讓洋腔洋調悄悄消失｜S3E20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tBhdEUDbAmw","https://www.youtube.com/watch?v=tBhdEUDbAmw")</f>
       </c>
       <c r="E5" s="2">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -890,31 +890,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pStoU9mSTYg</t>
+          <t>3NtAzWC9dVQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
+          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
       </c>
       <c r="E6" s="2">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -927,31 +927,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ob31JAy9EO0</t>
+          <t>4zqbHokYRiA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
+          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
       </c>
       <c r="E7" s="2">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -971,61 +971,61 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7ra5Zka3C2Y</t>
+          <t>pStoU9mSTYg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
+          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
       </c>
       <c r="E8" s="2">
-        <v>836</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E9" s="2">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1045,61 +1045,61 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E10" s="2">
-        <v>10</v>
+        <v>836</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1119,33 +1119,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E12" s="2">
-        <v>9785</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1156,24 +1156,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E13" s="2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1193,98 +1193,98 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E14" s="2">
-        <v>19</v>
+        <v>10099</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E15" s="2">
-        <v>1892</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E16" s="2">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1297,40 +1297,40 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E17" s="2">
-        <v>38</v>
+        <v>1899</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1341,61 +1341,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E18" s="2">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E19" s="2">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -1408,31 +1408,31 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E20" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -1441,35 +1441,35 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0357</v>
+        <v>0.0217</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E21" s="2">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -1489,24 +1489,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E22" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.037</v>
+        <v>0.0357</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1526,24 +1526,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E23" s="2">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -1563,33 +1563,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E24" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,24 +1600,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E25" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E26" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,24 +1674,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E27" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E28" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,33 +1748,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E29" s="2">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F29" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E30" s="2">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E31" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0063</v>
+        <v>0.0442</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,33 +1859,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E32" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.029</v>
+        <v>0.0128</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E33" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,24 +1933,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E34" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F34" s="2">
         <v>2</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.0465</v>
+        <v>0.029</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,24 +1970,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E35" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -2007,33 +2007,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E36" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F36" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E37" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E38" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E39" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,70 +2155,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E40" s="2">
-        <v>577</v>
+        <v>22</v>
       </c>
       <c r="F40" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0069</v>
+        <v>0.0455</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E41" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2229,33 +2229,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E42" s="2">
-        <v>92</v>
+        <v>579</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2266,33 +2266,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E43" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,24 +2303,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E44" s="2">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E45" s="2">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,33 +2377,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E46" s="2">
-        <v>348</v>
+        <v>85</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E47" s="2">
-        <v>441</v>
+        <v>272</v>
       </c>
       <c r="F47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,61 +2451,61 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E48" s="2">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="F48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E49" s="2">
-        <v>218</v>
+        <v>441</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0092</v>
+        <v>0.0045</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,70 +2525,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E50" s="2">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E51" s="2">
-        <v>1120</v>
+        <v>218</v>
       </c>
       <c r="F51" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0116</v>
+        <v>0.0092</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,33 +2599,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E52" s="2">
-        <v>702</v>
+        <v>280</v>
       </c>
       <c r="F52" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2636,33 +2636,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E53" s="2">
-        <v>979</v>
+        <v>1120</v>
       </c>
       <c r="F53" s="2">
+        <v>8</v>
+      </c>
+      <c r="G53" s="2">
         <v>5</v>
       </c>
-      <c r="G53" s="2">
-        <v>0</v>
-      </c>
       <c r="H53" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,33 +2673,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E54" s="2">
-        <v>71</v>
+        <v>702</v>
       </c>
       <c r="F54" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,33 +2710,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E55" s="2">
-        <v>181</v>
+        <v>979</v>
       </c>
       <c r="F55" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E56" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -2784,24 +2784,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E57" s="2">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -2821,24 +2821,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E58" s="2">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -2851,31 +2851,31 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E59" s="2">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2888,19 +2888,19 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E60" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2932,12 +2932,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2946,19 +2946,19 @@
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E61" s="2">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2969,12 +2969,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E62" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -3006,12 +3006,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3020,19 +3020,19 @@
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,24 +3043,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E64" s="2">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -3073,68 +3073,68 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E65" s="2">
-        <v>679</v>
+        <v>2</v>
       </c>
       <c r="F65" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E66" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -3147,40 +3147,40 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E67" s="2">
-        <v>1111</v>
+        <v>679</v>
       </c>
       <c r="F67" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3191,33 +3191,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E68" s="2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3228,33 +3228,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E69" s="2">
-        <v>1186</v>
+        <v>1111</v>
       </c>
       <c r="F69" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G69" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0126</v>
+        <v>0.0027</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,33 +3265,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E70" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,33 +3302,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E71" s="2">
-        <v>403</v>
+        <v>1186</v>
       </c>
       <c r="F71" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G71" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0099</v>
+        <v>0.0126</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,24 +3339,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E72" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -3369,40 +3369,40 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E73" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,33 +3413,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E74" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3450,33 +3450,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E75" s="2">
-        <v>1027</v>
+        <v>116</v>
       </c>
       <c r="F75" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,33 +3487,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E76" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,33 +3524,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E77" s="2">
-        <v>197</v>
+        <v>1027</v>
       </c>
       <c r="F77" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,24 +3561,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E78" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -3591,19 +3591,19 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -3628,19 +3628,19 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3649,130 +3649,130 @@
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E80" s="2">
-        <v>1134</v>
+        <v>3</v>
       </c>
       <c r="F80" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E81" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F81" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E82" s="2">
-        <v>17</v>
+        <v>1134</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E83" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F83" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3783,24 +3783,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E84" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -3813,77 +3813,77 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E85" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E86" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F86" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3894,24 +3894,24 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E87" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F87" s="2">
         <v>1</v>
@@ -3920,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0541</v>
+        <v>0.0513</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3931,33 +3931,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E88" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F88" s="2">
+        <v>3</v>
+      </c>
+      <c r="G88" s="2">
         <v>1</v>
       </c>
-      <c r="G88" s="2">
-        <v>0</v>
-      </c>
       <c r="H88" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,70 +3968,70 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E89" s="2">
-        <v>1317</v>
+        <v>37</v>
       </c>
       <c r="F89" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E90" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,144 +4042,144 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E91" s="2">
-        <v>45</v>
+        <v>1317</v>
       </c>
       <c r="F91" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0444</v>
+        <v>0.0114</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E92" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F92" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E93" s="2">
-        <v>531</v>
+        <v>45</v>
       </c>
       <c r="F93" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0094</v>
+        <v>0.0444</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E94" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F94" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4190,33 +4190,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E95" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F95" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4227,24 +4227,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E96" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F96" s="2">
         <v>1</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.027</v>
+        <v>0.0213</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,33 +4264,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E97" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,107 +4301,107 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E98" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.0294</v>
+        <v>0.027</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E99" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6pWGpIUBSBs</t>
+          <t>8__o_r_dr4M</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>孩子不是等會了才開始是開始了才會  #shorts</t>
+          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>10/16/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6pWGpIUBSBs","https://www.youtube.com/watch?v=6pWGpIUBSBs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
       </c>
       <c r="E100" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F100" s="2">
         <v>1</v>
       </c>
       <c r="G100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0196</v>
+        <v>0.0294</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4412,24 +4412,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5eDsf75XtOg</t>
+          <t>D3J2PrJtgxQ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>每天 10 分鐘故事時間孩子從不想讀到主動愛上中文 #shorts</t>
+          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5eDsf75XtOg","https://www.youtube.com/watch?v=5eDsf75XtOg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
       </c>
       <c r="E101" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F101" s="2">
         <v>0</v>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5344,7 +5344,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B5" s="2">

--- a/youtube_reports/YouTube_Comment_Insights_latest.xlsx
+++ b/youtube_reports/YouTube_Comment_Insights_latest.xlsx
@@ -155,7 +155,7 @@
         <v>Channel subscribers</v>
       </c>
       <c r="B4" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C4" s="2">
         <v>Public YouTube channel subscriber count</v>
@@ -177,7 +177,7 @@
         <v>Comments fetched</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>Public comments from exported videos</v>
@@ -199,7 +199,7 @@
         <v>Public views total</v>
       </c>
       <c r="B6" s="2">
-        <v>32730</v>
+        <v>33116</v>
       </c>
       <c r="C6" s="2">
         <v/>
@@ -243,7 +243,7 @@
         <v>Public comments total</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2">
         <v/>
@@ -265,7 +265,7 @@
         <v>Videos with comments</v>
       </c>
       <c r="B9" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
         <v/>
@@ -400,7 +400,7 @@
         <v>和樂樂一起唱讀｜媽媽媽媽在哪裡?</v>
       </c>
       <c r="C15" s="2">
-        <v>10099</v>
+        <v>10353</v>
       </c>
       <c r="D15" s="2">
         <v>28</v>
@@ -420,7 +420,7 @@
         <v>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</v>
       </c>
       <c r="C16" s="2">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
@@ -520,7 +520,7 @@
         <v>我的母語是什麼 #shorts</v>
       </c>
       <c r="C21" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D21" s="2">
         <v>8</v>
@@ -644,10 +644,10 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>18960</v>
+        <v>18947</v>
       </c>
       <c r="D27" s="2">
-        <v>305.8</v>
+        <v>305.6</v>
       </c>
       <c r="E27" s="2">
         <v/>
@@ -666,10 +666,10 @@
         <v>38</v>
       </c>
       <c r="C28" s="2">
-        <v>13770</v>
+        <v>14169</v>
       </c>
       <c r="D28" s="2">
-        <v>362.4</v>
+        <v>372.9</v>
       </c>
       <c r="E28" s="2">
         <v/>
@@ -749,24 +749,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vlS7Rmbj20s</t>
+          <t>5igZAJZvIW4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Emma 在家裡沒有中文環境，自己也不會中文，卻陪孩子讀完樂樂紅、黃、綠書 300 本！ #shorts</t>
+          <t>父母就是孩子最好的老師，因為沒有人比你更了解他 #shorts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>08/15/2026</t>
         </is>
       </c>
       <c r="D2" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=vlS7Rmbj20s","https://www.youtube.com/watch?v=vlS7Rmbj20s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5igZAJZvIW4","https://www.youtube.com/watch?v=5igZAJZvIW4")</f>
       </c>
       <c r="E2" s="2">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -786,33 +786,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>goe-UOeBrOU</t>
+          <t>tnvwPuPCceg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜顏色朋友歌</t>
+          <t>059｜【樂樂 Talk】海外孩子要打的小一大魔王——中英夾雜、說錯話，家長怎麼應對才不會搞砸？｜S3E21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="D3" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=goe-UOeBrOU","https://www.youtube.com/watch?v=goe-UOeBrOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tnvwPuPCceg","https://www.youtube.com/watch?v=tnvwPuPCceg")</f>
       </c>
       <c r="E3" s="2">
-        <v>384</v>
+        <v>135</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.0052</v>
+        <v>0.0074</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -823,33 +823,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>81z7sy7UCoU</t>
+          <t>vlS7Rmbj20s</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>困難不在外面，而在心裡 ❤️ 一旦決定了，每個問題都有解方 #shorts</t>
+          <t>Emma 在家裡沒有中文環境，自己也不會中文，卻陪孩子讀完樂樂紅、黃、綠書 300 本！ #shorts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="D4" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=81z7sy7UCoU","https://www.youtube.com/watch?v=81z7sy7UCoU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=vlS7Rmbj20s","https://www.youtube.com/watch?v=vlS7Rmbj20s")</f>
       </c>
       <c r="E4" s="2">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0.0078</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -860,33 +860,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tBhdEUDbAmw</t>
+          <t>goe-UOeBrOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>057｜【樂樂 Talk】孩子有自我修正的能力——大量聽讀如何讓洋腔洋調悄悄消失｜S3E20</t>
+          <t>和樂樂一起唱讀｜五顏六色</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07/28/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="D5" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tBhdEUDbAmw","https://www.youtube.com/watch?v=tBhdEUDbAmw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=goe-UOeBrOU","https://www.youtube.com/watch?v=goe-UOeBrOU")</f>
       </c>
       <c r="E5" s="2">
-        <v>58</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -897,33 +897,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3NtAzWC9dVQ</t>
+          <t>81z7sy7UCoU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
+          <t>困難不在外面，而在心裡 ❤️ 一旦決定了，每個問題都有解方 #shorts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07/25/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="D6" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=81z7sy7UCoU","https://www.youtube.com/watch?v=81z7sy7UCoU")</f>
       </c>
       <c r="E6" s="2">
-        <v>241</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -934,24 +934,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4zqbHokYRiA</t>
+          <t>tBhdEUDbAmw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
+          <t>057｜【樂樂 Talk】孩子有自我修正的能力——大量聽讀如何讓洋腔洋調悄悄消失｜S3E20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>07/18/2026</t>
+          <t>07/28/2026</t>
         </is>
       </c>
       <c r="D7" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tBhdEUDbAmw","https://www.youtube.com/watch?v=tBhdEUDbAmw")</f>
       </c>
       <c r="E7" s="2">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -964,31 +964,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pStoU9mSTYg</t>
+          <t>3NtAzWC9dVQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
+          <t>我們能創造「不得不用」的機會，孩子就有可能把中文留住 #shorts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07/14/2026</t>
+          <t>07/25/2026</t>
         </is>
       </c>
       <c r="D8" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=3NtAzWC9dVQ","https://www.youtube.com/watch?v=3NtAzWC9dVQ")</f>
       </c>
       <c r="E8" s="2">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1001,31 +1001,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ob31JAy9EO0</t>
+          <t>4zqbHokYRiA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
+          <t>愛上故事、讀懂內容，語感與字音會在反覆閱讀中自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/18/2026</t>
         </is>
       </c>
       <c r="D9" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4zqbHokYRiA","https://www.youtube.com/watch?v=4zqbHokYRiA")</f>
       </c>
       <c r="E9" s="2">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1045,61 +1045,61 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7ra5Zka3C2Y</t>
+          <t>pStoU9mSTYg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
+          <t>055｜【樂樂 Talk】樂樂300本念完能有多少字彙量？——問錯問題，就會走上錯的路｜S3E19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>07/11/2026</t>
+          <t>07/14/2026</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pStoU9mSTYg","https://www.youtube.com/watch?v=pStoU9mSTYg")</f>
       </c>
       <c r="E10" s="2">
-        <v>836</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2lniaAlT6Vs</t>
+          <t>ob31JAy9EO0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
+          <t>📍 台北世貿一館 C533 🗓️ 2026年7月 12-14日 #shorts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ob31JAy9EO0","https://www.youtube.com/watch?v=ob31JAy9EO0")</f>
       </c>
       <c r="E11" s="2">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1119,61 +1119,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kp9M8t54t0M</t>
+          <t>7ra5Zka3C2Y</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
+          <t>孩子學母語，同時也在守護他們的心理健康✨ #shorts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06/30/2026</t>
+          <t>07/11/2026</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=7ra5Zka3C2Y","https://www.youtube.com/watch?v=7ra5Zka3C2Y")</f>
       </c>
       <c r="E12" s="2">
-        <v>11</v>
+        <v>836</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bdtcmxka_MY</t>
+          <t>2lniaAlT6Vs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
+          <t>會說中文，和教孩子中文，是兩件不同的事。請善待自己，給自己一點空間。 #shorts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2lniaAlT6Vs","https://www.youtube.com/watch?v=2lniaAlT6Vs")</f>
       </c>
       <c r="E13" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1193,33 +1193,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>uIh_eS18B1g</t>
+          <t>Kp9M8t54t0M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡?</t>
+          <t>053｜【樂樂 Talk】如果你用繪本標準看樂樂，這一集可能會顛覆你——圖文設計背後的學習科學｜S3E18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>06/30/2026</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kp9M8t54t0M","https://www.youtube.com/watch?v=Kp9M8t54t0M")</f>
       </c>
       <c r="E14" s="2">
-        <v>10099</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1230,24 +1230,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>40hJk3-ng3U</t>
+          <t>Bdtcmxka_MY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>端午兒歌-讓孩子記得端午 #shorts</t>
+          <t>文字不是冷冰冰的符號，當它出現在故事裡，就會變成孩子的朋友 #shorts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Bdtcmxka_MY","https://www.youtube.com/watch?v=Bdtcmxka_MY")</f>
       </c>
       <c r="E15" s="2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -1267,98 +1267,98 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mi5VfA4LjIA</t>
+          <t>uIh_eS18B1g</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
+          <t>和樂樂一起唱讀｜媽媽媽媽在哪裡?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/20/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uIh_eS18B1g","https://www.youtube.com/watch?v=uIh_eS18B1g")</f>
       </c>
       <c r="E16" s="2">
-        <v>19</v>
+        <v>10353</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YWZkP3iOrDo</t>
+          <t>40hJk3-ng3U</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
+          <t>端午兒歌-讓孩子記得端午 #shorts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=40hJk3-ng3U","https://www.youtube.com/watch?v=40hJk3-ng3U")</f>
       </c>
       <c r="E17" s="2">
-        <v>1899</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R5yyhHk-J0s</t>
+          <t>Mi5VfA4LjIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
+          <t>樂樂書裡(紅59_媽媽)的故事連結家長與孩子的溫馨回憶 #shorts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/19/2026</t>
+          <t>06/20/2026</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Mi5VfA4LjIA","https://www.youtube.com/watch?v=Mi5VfA4LjIA")</f>
       </c>
       <c r="E18" s="2">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1371,40 +1371,40 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>_JKtuITH1EU</t>
+          <t>YWZkP3iOrDo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
+          <t>和樂樂一起唱讀｜端午兒歌 Dragon Boat Song</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YWZkP3iOrDo","https://www.youtube.com/watch?v=YWZkP3iOrDo")</f>
       </c>
       <c r="E19" s="2">
-        <v>39</v>
+        <v>1902</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1415,61 +1415,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tWX11sxfSL8</t>
+          <t>R5yyhHk-J0s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
+          <t>和樂樂一起唱讀｜爸爸的東西在哪裡？</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>06/13/2026</t>
+          <t>06/19/2026</t>
         </is>
       </c>
       <c r="D20" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5yyhHk-J0s","https://www.youtube.com/watch?v=R5yyhHk-J0s")</f>
       </c>
       <c r="E20" s="2">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFvmvuO_HfY</t>
+          <t>_JKtuITH1EU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
+          <t>051｜【樂樂 Talk】一代移民的孩子，怎麼在雙語中長大——擁有最強中文資源，卻最容易失敗的原因｜S3E17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="D21" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_JKtuITH1EU","https://www.youtube.com/watch?v=_JKtuITH1EU")</f>
       </c>
       <c r="E21" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -1482,31 +1482,31 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1WZbykZn8xM</t>
+          <t>tWX11sxfSL8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
+          <t>讓孩子讀喜歡的書 重點是要持續享受閱讀 #shorts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>06/13/2026</t>
         </is>
       </c>
       <c r="D22" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tWX11sxfSL8","https://www.youtube.com/watch?v=tWX11sxfSL8")</f>
       </c>
       <c r="E22" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
@@ -1515,35 +1515,35 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.0357</v>
+        <v>0.0217</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I4LBpvuZHmE</t>
+          <t>SFvmvuO_HfY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
+          <t>不是靠技巧，而是大人先能感受、體會、享受其中 #shorts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>05/30/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="D23" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SFvmvuO_HfY","https://www.youtube.com/watch?v=SFvmvuO_HfY")</f>
       </c>
       <c r="E23" s="2">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -1563,24 +1563,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G0pBnvlFHko</t>
+          <t>1WZbykZn8xM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
+          <t>049｜【樂樂 Talk】當孩子中文進步太快——另一半焦慮、當地語言退步了怎麼辦？｜S3E16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D24" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=1WZbykZn8xM","https://www.youtube.com/watch?v=1WZbykZn8xM")</f>
       </c>
       <c r="E24" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0.037</v>
+        <v>0.0357</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1600,24 +1600,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M_oWZ54-bns</t>
+          <t>I4LBpvuZHmE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
+          <t>腦袋遠比我們想像得更能承載多語 #shorts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>05/30/2026</t>
         </is>
       </c>
       <c r="D25" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=I4LBpvuZHmE","https://www.youtube.com/watch?v=I4LBpvuZHmE")</f>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -1637,33 +1637,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NKCd10Go2mE</t>
+          <t>G0pBnvlFHko</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
+          <t>048｜【樂樂 Talk】為什麼孩子只想重複讀同一本書？——把書藏到衣櫃裡，Jewel 的真實告白｜S4E05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D26" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G0pBnvlFHko","https://www.youtube.com/watch?v=G0pBnvlFHko")</f>
       </c>
       <c r="E26" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1674,24 +1674,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a6Bm-ftleDM</t>
+          <t>M_oWZ54-bns</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>重複，是最自然的學習方式 #shorts</t>
+          <t>原來孩子放棄中文的真正原因是....壓力🦆 #shorts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>05/23/2026</t>
         </is>
       </c>
       <c r="D27" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M_oWZ54-bns","https://www.youtube.com/watch?v=M_oWZ54-bns")</f>
       </c>
       <c r="E27" s="2">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
@@ -1711,33 +1711,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gBLovSpZ-Eo</t>
+          <t>NKCd10Go2mE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
+          <t>047｜【樂樂 Talk】為什麼孩子只看圖不看字？——放下識字焦慮，看圖才是閱讀真正的起點｜S3E15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="D28" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NKCd10Go2mE","https://www.youtube.com/watch?v=NKCd10Go2mE")</f>
       </c>
       <c r="E28" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1748,24 +1748,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L7yqvCALW_I</t>
+          <t>a6Bm-ftleDM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
+          <t>重複，是最自然的學習方式 #shorts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="D29" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=a6Bm-ftleDM","https://www.youtube.com/watch?v=a6Bm-ftleDM")</f>
       </c>
       <c r="E29" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
@@ -1785,33 +1785,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rIAHgQuHq2Q</t>
+          <t>gBLovSpZ-Eo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
+          <t>046｜【樂樂 Talk】為什麼孩子只要我讀？——孩子不肯自己讀，其實是最好的訊號｜S4E04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="D30" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gBLovSpZ-Eo","https://www.youtube.com/watch?v=gBLovSpZ-Eo")</f>
       </c>
       <c r="E30" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1822,33 +1822,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NxeVOWfGP-k</t>
+          <t>L7yqvCALW_I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>一次購入 300 本樂樂書，和一群家庭持續 2–3 年共讀，孩子在幸福的環境裡自然走向獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="D31" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=L7yqvCALW_I","https://www.youtube.com/watch?v=L7yqvCALW_I")</f>
       </c>
       <c r="E31" s="2">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F31" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1859,33 +1859,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Toc1mr7KORw</t>
+          <t>rIAHgQuHq2Q</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
+          <t>045｜【樂樂 Talk】每天10分鐘，夠嗎？——從跳繩實驗到三歲半突然自己讀完一本書｜S3E13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/28/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D32" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rIAHgQuHq2Q","https://www.youtube.com/watch?v=rIAHgQuHq2Q")</f>
       </c>
       <c r="E32" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1896,33 +1896,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SQ781eMsfG0</t>
+          <t>NxeVOWfGP-k</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04/25/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D33" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=NxeVOWfGP-k","https://www.youtube.com/watch?v=NxeVOWfGP-k")</f>
       </c>
       <c r="E33" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0.0063</v>
+        <v>0.0442</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1933,33 +1933,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CGnUHEeHlts</t>
+          <t>Toc1mr7KORw</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
+          <t>044｜【樂樂 Talk】為什麼閱讀比會說更重要？——海外家庭守護中文最需要知道的一件事｜S403</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04/21/2026</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="D34" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Toc1mr7KORw","https://www.youtube.com/watch?v=Toc1mr7KORw")</f>
       </c>
       <c r="E34" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="3">
-        <v>0.029</v>
+        <v>0.0128</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1970,33 +1970,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HFMQYNCYQw8</t>
+          <t>SQ781eMsfG0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
+          <t>🤔明明 6 歲前會雙語，為什麼一上學就不再說中文？ #shorts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>04/25/2026</t>
         </is>
       </c>
       <c r="D35" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=SQ781eMsfG0","https://www.youtube.com/watch?v=SQ781eMsfG0")</f>
       </c>
       <c r="E35" s="2">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2007,24 +2007,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6kQxIMwsbKU</t>
+          <t>CGnUHEeHlts</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
+          <t>043｜【樂樂 Talk】共讀挑戰存在的理由——不是為了完美達成，而是為了讓你不再一個人撐｜S3E13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="D36" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=CGnUHEeHlts","https://www.youtube.com/watch?v=CGnUHEeHlts")</f>
       </c>
       <c r="E36" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F36" s="2">
         <v>2</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="3">
-        <v>0.0465</v>
+        <v>0.029</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2044,24 +2044,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MY91MQwmI1A</t>
+          <t>HFMQYNCYQw8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
+          <t>能講中文給孩子聽的，可能只有你。一旦錯過黃金期，中文就真的回不來。 💔 #shorts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="D37" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=HFMQYNCYQw8","https://www.youtube.com/watch?v=HFMQYNCYQw8")</f>
       </c>
       <c r="E37" s="2">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -2081,33 +2081,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dqYgH8is3JQ</t>
+          <t>6kQxIMwsbKU</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
+          <t>042｜【樂樂 Talk】比較，會讓你忘記為什麼出發——寫給每個走得很累的海外家長｜S4E02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="D38" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=6kQxIMwsbKU","https://www.youtube.com/watch?v=6kQxIMwsbKU")</f>
       </c>
       <c r="E38" s="2">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="3">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2118,24 +2118,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>G8NUQP4Kf84</t>
+          <t>MY91MQwmI1A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
+          <t>語言一旦失去，不只是工具的消失，還會在親子心裡的溝通上，再多拉開一層距離 #shorts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="D39" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MY91MQwmI1A","https://www.youtube.com/watch?v=MY91MQwmI1A")</f>
       </c>
       <c r="E39" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -2155,33 +2155,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QhEIUvMJso8</t>
+          <t>dqYgH8is3JQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
+          <t>041｜【樂樂 Talk】不是缺資源，而是缺陪伴——海外家庭為什麼需要訂閱電子報？｜S3E12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="D40" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=dqYgH8is3JQ","https://www.youtube.com/watch?v=dqYgH8is3JQ")</f>
       </c>
       <c r="E40" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2192,24 +2192,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aAzQfQmMr30</t>
+          <t>G8NUQP4Kf84</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
+          <t>了解自己的母語文化 讓孩子對自己的身份感到驕傲 #shorts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>03/28/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D41" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=G8NUQP4Kf84","https://www.youtube.com/watch?v=G8NUQP4Kf84")</f>
       </c>
       <c r="E41" s="2">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -2229,70 +2229,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cbWBjTNHMlg</t>
+          <t>QhEIUvMJso8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
+          <t>040｜【樂樂 Talk】孩子聽得懂中文卻不說？比起教導，他們更需要的是「安全感」</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03/21/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="D42" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QhEIUvMJso8","https://www.youtube.com/watch?v=QhEIUvMJso8")</f>
       </c>
       <c r="E42" s="2">
-        <v>579</v>
+        <v>22</v>
       </c>
       <c r="F42" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0.0069</v>
+        <v>0.0455</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RmtECKEzgdk</t>
+          <t>aAzQfQmMr30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
+          <t>語言不是天賦，而是輸入＋陪伴的奇蹟。❤️ #shorts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>03/14/2026</t>
+          <t>03/28/2026</t>
         </is>
       </c>
       <c r="D43" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=aAzQfQmMr30","https://www.youtube.com/watch?v=aAzQfQmMr30")</f>
       </c>
       <c r="E43" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2303,33 +2303,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RRiEw9GirF8</t>
+          <t>cbWBjTNHMlg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
+          <t>交給老師教中文，你就會錯過這些可愛又珍貴的時刻 #shorts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>03/21/2026</t>
         </is>
       </c>
       <c r="D44" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=cbWBjTNHMlg","https://www.youtube.com/watch?v=cbWBjTNHMlg")</f>
       </c>
       <c r="E44" s="2">
-        <v>92</v>
+        <v>579</v>
       </c>
       <c r="F44" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2340,33 +2340,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>k-Gvh-W3448</t>
+          <t>RmtECKEzgdk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
+          <t>困難很多時候不是實際的，而是心理上的 #shorts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/14/2026</t>
         </is>
       </c>
       <c r="D45" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RmtECKEzgdk","https://www.youtube.com/watch?v=RmtECKEzgdk")</f>
       </c>
       <c r="E45" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="F45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0.0089</v>
+        <v>0.025</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2377,24 +2377,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DNlMgiRfvVI</t>
+          <t>RRiEw9GirF8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>慢下來，孩子才跟得上你。 #shorts</t>
+          <t>📖 閱讀識字不一樣，孩子自己感興趣、自己想重複看的故事 #shorts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>02/26/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="D46" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RRiEw9GirF8","https://www.youtube.com/watch?v=RRiEw9GirF8")</f>
       </c>
       <c r="E46" s="2">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -2414,33 +2414,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tATGsjDBIho</t>
+          <t>k-Gvh-W3448</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
+          <t>閱讀能夠幫助孩子增加中文詞彙 #shorts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="D47" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=k-Gvh-W3448","https://www.youtube.com/watch?v=k-Gvh-W3448")</f>
       </c>
       <c r="E47" s="2">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="F47" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2451,33 +2451,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>156lKiWLNpc</t>
+          <t>DNlMgiRfvVI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
+          <t>慢下來，孩子才跟得上你。 #shorts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02/19/2026</t>
+          <t>02/26/2026</t>
         </is>
       </c>
       <c r="D48" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=DNlMgiRfvVI","https://www.youtube.com/watch?v=DNlMgiRfvVI")</f>
       </c>
       <c r="E48" s="2">
-        <v>348</v>
+        <v>85</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2488,33 +2488,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rsikARYbt_k</t>
+          <t>tATGsjDBIho</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臘月二十三到二十九的習俗 #shorts</t>
+          <t>親子共讀不是功課，而是點燃孩子 內在動力 的機會 🚗 #shorts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>02/16/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="D49" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tATGsjDBIho","https://www.youtube.com/watch?v=tATGsjDBIho")</f>
       </c>
       <c r="E49" s="2">
-        <v>441</v>
+        <v>272</v>
       </c>
       <c r="F49" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2525,61 +2525,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fqd1rkZOBXI</t>
+          <t>156lKiWLNpc</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lunar New Year overseas can feel quiet.</t>
+          <t>孩子最需要的不是補習班而是一個願意陪他聊天陪他過日子的爸媽 #shorts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/19/2026</t>
         </is>
       </c>
       <c r="D50" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=156lKiWLNpc","https://www.youtube.com/watch?v=156lKiWLNpc")</f>
       </c>
       <c r="E50" s="2">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4KwbOuflvnM</t>
+          <t>rsikARYbt_k</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>無壓力無目的只因為喜歡  #shorts</t>
+          <t>臘月二十三到二十九的習俗 #shorts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>02/14/2026</t>
+          <t>02/16/2026</t>
         </is>
       </c>
       <c r="D51" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=rsikARYbt_k","https://www.youtube.com/watch?v=rsikARYbt_k")</f>
       </c>
       <c r="E51" s="2">
-        <v>218</v>
+        <v>441</v>
       </c>
       <c r="F51" s="2">
         <v>2</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="3">
-        <v>0.0092</v>
+        <v>0.0045</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2599,70 +2599,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>YOQ_YMDduG4</t>
+          <t>fqd1rkZOBXI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>語言不是命令而是互動 #shorts</t>
+          <t>Lunar New Year overseas can feel quiet.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D52" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fqd1rkZOBXI","https://www.youtube.com/watch?v=fqd1rkZOBXI")</f>
       </c>
       <c r="E52" s="2">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COr7Y8WQolA</t>
+          <t>4KwbOuflvnM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>我的母語是什麼 #shorts</t>
+          <t>無壓力無目的只因為喜歡  #shorts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>02/14/2026</t>
         </is>
       </c>
       <c r="D53" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4KwbOuflvnM","https://www.youtube.com/watch?v=4KwbOuflvnM")</f>
       </c>
       <c r="E53" s="2">
-        <v>1120</v>
+        <v>218</v>
       </c>
       <c r="F53" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>0.0116</v>
+        <v>0.0092</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2673,33 +2673,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>v-UeHLv5PPE</t>
+          <t>YOQ_YMDduG4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
+          <t>語言不是命令而是互動 #shorts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="D54" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=YOQ_YMDduG4","https://www.youtube.com/watch?v=YOQ_YMDduG4")</f>
       </c>
       <c r="E54" s="2">
-        <v>702</v>
+        <v>280</v>
       </c>
       <c r="F54" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>0.0043</v>
+        <v>0.0036</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2710,33 +2710,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0kqFdl85Ovw</t>
+          <t>COr7Y8WQolA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
+          <t>我的母語是什麼 #shorts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/31/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D55" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=COr7Y8WQolA","https://www.youtube.com/watch?v=COr7Y8WQolA")</f>
       </c>
       <c r="E55" s="2">
-        <v>979</v>
+        <v>1121</v>
       </c>
       <c r="F55" s="2">
+        <v>8</v>
+      </c>
+      <c r="G55" s="2">
         <v>5</v>
       </c>
-      <c r="G55" s="2">
-        <v>0</v>
-      </c>
       <c r="H55" s="3">
-        <v>0.0051</v>
+        <v>0.0116</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2747,33 +2747,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5JMh-u137xw</t>
+          <t>v-UeHLv5PPE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
+          <t>樂樂親子讀書會  孩子們有人聽有人回應中文自然就說出口 #shorts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/29/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D56" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=v-UeHLv5PPE","https://www.youtube.com/watch?v=v-UeHLv5PPE")</f>
       </c>
       <c r="E56" s="2">
-        <v>71</v>
+        <v>702</v>
       </c>
       <c r="F56" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2784,33 +2784,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>uXXsvJp9qVY</t>
+          <t>0kqFdl85Ovw</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
+          <t>真正重要的不是字數而是他能不能讀懂故事 #shorts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>01/31/2026</t>
         </is>
       </c>
       <c r="D57" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kqFdl85Ovw","https://www.youtube.com/watch?v=0kqFdl85Ovw")</f>
       </c>
       <c r="E57" s="2">
-        <v>181</v>
+        <v>979</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2821,24 +2821,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oi1GS6VapWE</t>
+          <t>5JMh-u137xw</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
+          <t>孩子先在故事裡聽懂整句再透過重複自然記住字 #shorts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/17/2026</t>
+          <t>01/29/2026</t>
         </is>
       </c>
       <c r="D58" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=5JMh-u137xw","https://www.youtube.com/watch?v=5JMh-u137xw")</f>
       </c>
       <c r="E58" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -2858,24 +2858,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tEPnXhdLNJE</t>
+          <t>uXXsvJp9qVY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Untitled #shorts</t>
+          <t>中文不是一夕之功而是每天一點一滴的累積 #shorts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/15/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="D59" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=uXXsvJp9qVY","https://www.youtube.com/watch?v=uXXsvJp9qVY")</f>
       </c>
       <c r="E59" s="2">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -2895,24 +2895,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Xb8wSpTmcOU</t>
+          <t>Oi1GS6VapWE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>提供孩子學習環境, 給孩子成長的空間</t>
+          <t>Iris別糾結孩子有沒有指讀讀對聲音有時候他眼睛已經懂了只是嘴巴還跟不上 #shorts</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/17/2026</t>
         </is>
       </c>
       <c r="D60" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Oi1GS6VapWE","https://www.youtube.com/watch?v=Oi1GS6VapWE")</f>
       </c>
       <c r="E60" s="2">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -2925,31 +2925,31 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fMv8LZmuG8Y</t>
+          <t>tEPnXhdLNJE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
+          <t>Untitled #shorts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>01/15/2026</t>
         </is>
       </c>
       <c r="D61" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tEPnXhdLNJE","https://www.youtube.com/watch?v=tEPnXhdLNJE")</f>
       </c>
       <c r="E61" s="2">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -2962,19 +2962,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FEVbfZa_8bo</t>
+          <t>Xb8wSpTmcOU</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>母語是連結父母與孩子內心的一道橋</t>
+          <t>提供孩子學習環境, 給孩子成長的空間</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="D62" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Xb8wSpTmcOU","https://www.youtube.com/watch?v=Xb8wSpTmcOU")</f>
       </c>
       <c r="E62" s="2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -3006,12 +3006,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QzYo0YtN424</t>
+          <t>fMv8LZmuG8Y</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
+          <t>樂樂書的編排有很多細節能讓孩子一讀再讀, 每次都有新發現</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3020,19 +3020,19 @@
         </is>
       </c>
       <c r="D63" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=fMv8LZmuG8Y","https://www.youtube.com/watch?v=fMv8LZmuG8Y")</f>
       </c>
       <c r="E63" s="2">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3043,12 +3043,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4iFdEAlDjsg</t>
+          <t>FEVbfZa_8bo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
+          <t>母語是連結父母與孩子內心的一道橋</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D64" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FEVbfZa_8bo","https://www.youtube.com/watch?v=FEVbfZa_8bo")</f>
       </c>
       <c r="E64" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -3080,12 +3080,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R5EPlLtmDFU</t>
+          <t>QzYo0YtN424</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
+          <t>用故事書有趣的內容來驅使孩子主動閱讀</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3094,19 +3094,19 @@
         </is>
       </c>
       <c r="D65" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=QzYo0YtN424","https://www.youtube.com/watch?v=QzYo0YtN424")</f>
       </c>
       <c r="E65" s="2">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3117,24 +3117,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ho-BKFw-4TU</t>
+          <t>4iFdEAlDjsg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
+          <t>樂樂書裡紅59 媽媽的故事連結家長與孩子的溫馨回憶</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D66" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=4iFdEAlDjsg","https://www.youtube.com/watch?v=4iFdEAlDjsg")</f>
       </c>
       <c r="E66" s="2">
-        <v>155</v>
+        <v>16</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -3147,68 +3147,68 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lmCPb9D-8ew</t>
+          <t>R5EPlLtmDFU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
+          <t>從小開始培養閱讀習慣, 養成孩子學習的內趨力</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="D67" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=R5EPlLtmDFU","https://www.youtube.com/watch?v=R5EPlLtmDFU")</f>
       </c>
       <c r="E67" s="2">
-        <v>679</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <v>0.0074</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>emScxUjYlR8</t>
+          <t>Ho-BKFw-4TU</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>如果你正在找一個能走得久的中文起點</t>
+          <t>Peggy 學習母語能幫助孩子建立身份認同 #shorts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D68" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Ho-BKFw-4TU","https://www.youtube.com/watch?v=Ho-BKFw-4TU")</f>
       </c>
       <c r="E68" s="2">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -3221,40 +3221,40 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2YXUzg9R--c</t>
+          <t>lmCPb9D-8ew</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>如何在海外創造必須用中文的環境 #shorts</t>
+          <t>語言是文化的載體是孩子與根連結的橋樑 #shorts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D69" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=lmCPb9D-8ew","https://www.youtube.com/watch?v=lmCPb9D-8ew")</f>
       </c>
       <c r="E69" s="2">
-        <v>1111</v>
+        <v>679</v>
       </c>
       <c r="F69" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <v>0.0027</v>
+        <v>0.0074</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3265,33 +3265,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8RA7VSaicpg</t>
+          <t>emScxUjYlR8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
+          <t>如果你正在找一個能走得久的中文起點</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D70" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=emScxUjYlR8","https://www.youtube.com/watch?v=emScxUjYlR8")</f>
       </c>
       <c r="E70" s="2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3302,33 +3302,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MPw_QotGKng</t>
+          <t>2YXUzg9R--c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>力玄華語對我的家族其實是外來語 #shorts</t>
+          <t>如何在海外創造必須用中文的環境 #shorts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12/27/2025</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D71" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=2YXUzg9R--c","https://www.youtube.com/watch?v=2YXUzg9R--c")</f>
       </c>
       <c r="E71" s="2">
-        <v>1186</v>
+        <v>1111</v>
       </c>
       <c r="F71" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G71" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>0.0126</v>
+        <v>0.0027</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3339,33 +3339,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>t7ZQGroTrjQ</t>
+          <t>8RA7VSaicpg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
+          <t>039｜【樂樂 Talk】我不是讀書的料——Ting 如何從不愛閱讀，走到書蟲一家的真實故事｜S1E16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12/23/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="D72" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=8RA7VSaicpg","https://www.youtube.com/watch?v=8RA7VSaicpg")</f>
       </c>
       <c r="E72" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3376,33 +3376,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tJ1sxf6SZlM</t>
+          <t>MPw_QotGKng</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
+          <t>力玄華語對我的家族其實是外來語 #shorts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
       <c r="D73" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=MPw_QotGKng","https://www.youtube.com/watch?v=MPw_QotGKng")</f>
       </c>
       <c r="E73" s="2">
-        <v>403</v>
+        <v>1186</v>
       </c>
       <c r="F73" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H73" s="3">
-        <v>0.0099</v>
+        <v>0.0126</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3413,24 +3413,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>oyk8-qEYwgo</t>
+          <t>t7ZQGroTrjQ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
+          <t>038｜【樂樂 Talk】搬去英國前，她把整套樂樂書一起帶走——Carmen 談在沒有中文語境的異國，如何為孩子打造穩定的閱讀環境｜S1E15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
       <c r="D74" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7ZQGroTrjQ","https://www.youtube.com/watch?v=t7ZQGroTrjQ")</f>
       </c>
       <c r="E74" s="2">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -3443,40 +3443,40 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>t7CnGcQd7GY</t>
+          <t>tJ1sxf6SZlM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
+          <t>Michelle 的孩子正在同時學廣東話和普通話 #shorts</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="D75" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=tJ1sxf6SZlM","https://www.youtube.com/watch?v=tJ1sxf6SZlM")</f>
       </c>
       <c r="E75" s="2">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <v>0</v>
+        <v>0.0099</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3487,33 +3487,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>M7uq5R98q8M</t>
+          <t>oyk8-qEYwgo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
+          <t>中文不用死背它可以透過故事語感陪伴自然長出來 #shorts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="D76" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=oyk8-qEYwgo","https://www.youtube.com/watch?v=oyk8-qEYwgo")</f>
       </c>
       <c r="E76" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <v>0.0093</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3524,33 +3524,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>As_rvS90u0U</t>
+          <t>t7CnGcQd7GY</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
+          <t>孩子接觸中文的機會會越來越少久了就失去能力 #shorts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="D77" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=t7CnGcQd7GY","https://www.youtube.com/watch?v=t7CnGcQd7GY")</f>
       </c>
       <c r="E77" s="2">
-        <v>1027</v>
+        <v>116</v>
       </c>
       <c r="F77" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3561,33 +3561,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yw_bDT7gSt0</t>
+          <t>M7uq5R98q8M</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
+          <t>孩子從不會到愛讀中文其實有方法 #shorts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="D78" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=M7uq5R98q8M","https://www.youtube.com/watch?v=M7uq5R98q8M")</f>
       </c>
       <c r="E78" s="2">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
+        <v>0.0093</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3598,33 +3598,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>gOBRGn0_VX4</t>
+          <t>As_rvS90u0U</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Black Friday Presale #shorts</t>
+          <t>沒有一個更好的老師因為父母就是最好的老師  #shorts</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="D79" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=As_rvS90u0U","https://www.youtube.com/watch?v=As_rvS90u0U")</f>
       </c>
       <c r="E79" s="2">
-        <v>197</v>
+        <v>1027</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3635,24 +3635,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ymINFPXWByw</t>
+          <t>yw_bDT7gSt0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
+          <t>BLACK FRIDAY PRESALE ENDS SOON #shorts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="D80" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=yw_bDT7gSt0","https://www.youtube.com/watch?v=yw_bDT7gSt0")</f>
       </c>
       <c r="E80" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -3665,19 +3665,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>pFv2fEXPmFI</t>
+          <t>gOBRGn0_VX4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
+          <t>Black Friday Presale #shorts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D81" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=gOBRGn0_VX4","https://www.youtube.com/watch?v=gOBRGn0_VX4")</f>
       </c>
       <c r="E81" s="2">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -3702,19 +3702,19 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>_UGl6HqIlRA</t>
+          <t>ymINFPXWByw</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
+          <t>🎬【聖誕節倒數共讀 開始前先看影片！】</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3723,130 +3723,130 @@
         </is>
       </c>
       <c r="D82" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ymINFPXWByw","https://www.youtube.com/watch?v=ymINFPXWByw")</f>
       </c>
       <c r="E82" s="2">
-        <v>1134</v>
+        <v>3</v>
       </c>
       <c r="F82" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ojf4YQ_zNt8</t>
+          <t>pFv2fEXPmFI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>學中文不是教材而是陪伴的時光 #shorts</t>
+          <t>🎄 聖誕倒數共讀活動即將開始! 會員專屬</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D83" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=pFv2fEXPmFI","https://www.youtube.com/watch?v=pFv2fEXPmFI")</f>
       </c>
       <c r="E83" s="2">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>XphPh6ReY8k</t>
+          <t>_UGl6HqIlRA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
+          <t>因為拼音只是拼讀孩子可能會念卻寫不出換到另一個故事又完全卡住 #shorts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11/25/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
       <c r="D84" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=_UGl6HqIlRA","https://www.youtube.com/watch?v=_UGl6HqIlRA")</f>
       </c>
       <c r="E84" s="2">
-        <v>18</v>
+        <v>1134</v>
       </c>
       <c r="F84" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0ixV5Z4wRbU</t>
+          <t>ojf4YQ_zNt8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
+          <t>學中文不是教材而是陪伴的時光 #shorts</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>11/22/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
       <c r="D85" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ojf4YQ_zNt8","https://www.youtube.com/watch?v=ojf4YQ_zNt8")</f>
       </c>
       <c r="E85" s="2">
-        <v>333</v>
+        <v>697</v>
       </c>
       <c r="F85" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3857,24 +3857,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FvesuyU_Cmk</t>
+          <t>XphPh6ReY8k</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>原來學中文不用一個人苦撐 #shorts</t>
+          <t>035｜【樂樂 Talk】孩子不缺知識，缺的是情感教育——明灑老師談共讀如何補足學校教育給不了的養分（下）｜S2E12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/25/2025</t>
         </is>
       </c>
       <c r="D86" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=XphPh6ReY8k","https://www.youtube.com/watch?v=XphPh6ReY8k")</f>
       </c>
       <c r="E86" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -3887,77 +3887,77 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RxVzs4HJBow</t>
+          <t>0ixV5Z4wRbU</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
+          <t>孩子在遊戲中參與在陪伴中快樂自然走向  獨立閱讀 #shorts</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/22/2025</t>
         </is>
       </c>
       <c r="D87" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0ixV5Z4wRbU","https://www.youtube.com/watch?v=0ixV5Z4wRbU")</f>
       </c>
       <c r="E87" s="2">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="F87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="3">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>anmOs42G-0I</t>
+          <t>FvesuyU_Cmk</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
+          <t>原來學中文不用一個人苦撐 #shorts</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="D88" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=FvesuyU_Cmk","https://www.youtube.com/watch?v=FvesuyU_Cmk")</f>
       </c>
       <c r="E88" s="2">
-        <v>1178</v>
+        <v>2</v>
       </c>
       <c r="F88" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3968,24 +3968,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ZFOGcVTpgiY</t>
+          <t>RxVzs4HJBow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
+          <t>034｜【樂樂 Talk】極簡共讀——明灑老師談大人的感受同樣重要，共讀不是任務，是享受（上）｜S2E11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="D89" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=RxVzs4HJBow","https://www.youtube.com/watch?v=RxVzs4HJBow")</f>
       </c>
       <c r="E89" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F89" s="2">
         <v>1</v>
@@ -3994,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="3">
-        <v>0.0541</v>
+        <v>0.0513</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4005,33 +4005,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0mruiiNyj9M</t>
+          <t>anmOs42G-0I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
+          <t>我們用上一代的方式去教中文卻讓孩子失去語言的感情 #shorts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="D90" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=anmOs42G-0I","https://www.youtube.com/watch?v=anmOs42G-0I")</f>
       </c>
       <c r="E90" s="2">
-        <v>211</v>
+        <v>1178</v>
       </c>
       <c r="F90" s="2">
+        <v>3</v>
+      </c>
+      <c r="G90" s="2">
         <v>1</v>
       </c>
-      <c r="G90" s="2">
-        <v>0</v>
-      </c>
       <c r="H90" s="3">
-        <v>0.0047</v>
+        <v>0.0034</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4042,70 +4042,70 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TOtqkJORHhg</t>
+          <t>ZFOGcVTpgiY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
+          <t>033｜【樂樂 Talk】孩子進了學校，母語使用率從100%掉到50%——力玄談如何在主流語言環境中為孩子築起母語的堡壘（下）｜S2E10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11/06/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="D91" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=ZFOGcVTpgiY","https://www.youtube.com/watch?v=ZFOGcVTpgiY")</f>
       </c>
       <c r="E91" s="2">
-        <v>1317</v>
+        <v>37</v>
       </c>
       <c r="F91" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="3">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>qgzJr7ZtvhE</t>
+          <t>0mruiiNyj9M</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
+          <t>沒有家庭輸入沒有和家人的中文連結再好的中文學校再多的課程也只是表面功夫 #shorts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>11/05/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="D92" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0mruiiNyj9M","https://www.youtube.com/watch?v=0mruiiNyj9M")</f>
       </c>
       <c r="E92" s="2">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4116,144 +4116,144 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9SQ9Vlq1RIc</t>
+          <t>TOtqkJORHhg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
+          <t>覺得自己中文不夠好就不敢陪孩子一起學嗎 #shorts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>11/06/2025</t>
         </is>
       </c>
       <c r="D93" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TOtqkJORHhg","https://www.youtube.com/watch?v=TOtqkJORHhg")</f>
       </c>
       <c r="E93" s="2">
-        <v>45</v>
+        <v>1317</v>
       </c>
       <c r="F93" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <v>0.0444</v>
+        <v>0.0114</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0kc4Dapw_To</t>
+          <t>qgzJr7ZtvhE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
+          <t>在樂樂學苑  孩子在 show  tell 裡分享自己怎麼念樂樂書 #shorts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="D94" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=qgzJr7ZtvhE","https://www.youtube.com/watch?v=qgzJr7ZtvhE")</f>
       </c>
       <c r="E94" s="2">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="F94" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iOcGa4QDSbs</t>
+          <t>9SQ9Vlq1RIc</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
+          <t>032｜【樂樂 Talk】什麼是母語？為什麼要為孩子保留它——台語路協會理事長力玄談母語傳承與找回的旅程（上）｜S2E09</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="D95" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=9SQ9Vlq1RIc","https://www.youtube.com/watch?v=9SQ9Vlq1RIc")</f>
       </c>
       <c r="E95" s="2">
-        <v>531</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="3">
-        <v>0.0094</v>
+        <v>0.0435</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VeX2IrkpDOE</t>
+          <t>0kc4Dapw_To</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
+          <t>一起看看樂樂家庭怎麼用閱讀讓中文變得有趣</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D96" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=0kc4Dapw_To","https://www.youtube.com/watch?v=0kc4Dapw_To")</f>
       </c>
       <c r="E96" s="2">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0.0213</v>
+        <v>0.0127</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4264,33 +4264,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kap_qkHuilM</t>
+          <t>iOcGa4QDSbs</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
+          <t>語言不只是技能而是家的溫度愛的鑰匙  #shorts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10/25/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="D97" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=iOcGa4QDSbs","https://www.youtube.com/watch?v=iOcGa4QDSbs")</f>
       </c>
       <c r="E97" s="2">
-        <v>184</v>
+        <v>531</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4301,24 +4301,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BxgMlfqRQIE</t>
+          <t>VeX2IrkpDOE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
+          <t>037｜【樂樂 Talk】孩子只想看漫畫，算閱讀嗎？——Peggy 談獨立閱讀後如何守住那份熱愛（下）｜S1E14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="D98" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=VeX2IrkpDOE","https://www.youtube.com/watch?v=VeX2IrkpDOE")</f>
       </c>
       <c r="E98" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F98" s="2">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <v>0.027</v>
+        <v>0.0208</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4338,33 +4338,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TMBYaTbci1k</t>
+          <t>Kap_qkHuilM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>只靠週末補中文真的不夠 #shorts</t>
+          <t>只要孩子建立了閱讀能力他就會變成一個自學機器人  #shorts</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10/18/2025</t>
+          <t>10/25/2025</t>
         </is>
       </c>
       <c r="D99" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=Kap_qkHuilM","https://www.youtube.com/watch?v=Kap_qkHuilM")</f>
       </c>
       <c r="E99" s="2">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="F99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4375,74 +4375,74 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8__o_r_dr4M</t>
+          <t>BxgMlfqRQIE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
+          <t>036｜【樂樂 Talk】本來只想說廣東話就夠了——Squeaky Dumplings Peggy 談身分認同、閱讀敏感期與讓中文成為生活的方法（上）｜S1E13</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10/16/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="D100" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=BxgMlfqRQIE","https://www.youtube.com/watch?v=BxgMlfqRQIE")</f>
       </c>
       <c r="E100" s="2">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="F100" s="2">
         <v>1</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0.0294</v>
+        <v>0.0256</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D3J2PrJtgxQ</t>
+          <t>TMBYaTbci1k</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>031｜【樂樂 Talk】點讀筆糾正了媽媽的發音——厚厚私塾 Iris 談中文遊戲與持續輸入的力量（下）｜S1E12</t>
+          <t>只靠週末補中文真的不夠 #shorts</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>10/18/2025</t>
         </is>
       </c>
       <c r="D101" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=D3J2PrJtgxQ","https://www.youtube.com/watch?v=D3J2PrJtgxQ")</f>
+        <f>HYPERLINK("https://www.youtube.com/watch?v=TMBYaTbci1k","https://www.youtube.com/watch?v=TMBYaTbci1k")</f>
       </c>
       <c r="E101" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5213,61 +5213,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8__o_r_dr4M</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>快樂閱讀才是孩子的語言之路 #shorts</t>
-        </is>
-      </c>
-      <c r="C15" s="4">
-        <f>HYPERLINK("https://www.youtube.com/watch?v=8__o_r_dr4M","https://www.youtube.com/watch?v=8__o_r_dr4M")</f>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>@annieyang6601</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>10/30/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>了解整套</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>未分類</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>可簡短感謝，觀察是否能延伸成下一支內容題材。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K14"/>
 </worksheet>
 </file>
 
@@ -5329,7 +5276,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>共讀與閱讀</t>
+          <t>海外環境</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5344,7 +5291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>海外環境</t>
+          <t>共讀與閱讀</t>
         </is>
       </c>
       <c r="B5" s="2">
